--- a/public/OpenSlot_AI_mock_database.xlsx
+++ b/public/OpenSlot_AI_mock_database.xlsx
@@ -11,9 +11,13 @@
     <sheet name="Calls" sheetId="6" r:id="rId6"/>
     <sheet name="Audit_Log" sheetId="7" r:id="rId7"/>
     <sheet name="Rules" sheetId="8" r:id="rId8"/>
-    <sheet name="Supabase_Mapping" sheetId="9" r:id="rId9"/>
-    <sheet name="Import_Readme" sheetId="10" r:id="rId10"/>
-    <sheet name="Sources" sheetId="11" r:id="rId11"/>
+    <sheet name="Services" sheetId="9" r:id="rId9"/>
+    <sheet name="Locations" sheetId="10" r:id="rId10"/>
+    <sheet name="Segments" sheetId="11" r:id="rId11"/>
+    <sheet name="Scoring" sheetId="12" r:id="rId12"/>
+    <sheet name="Supabase_Mapping" sheetId="13" r:id="rId13"/>
+    <sheet name="Import_Readme" sheetId="14" r:id="rId14"/>
+    <sheet name="Sources" sheetId="15" r:id="rId15"/>
   </sheets>
 </workbook>
 </file>
@@ -407,7 +411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -479,15 +483,451 @@
         <v>no blocked calls</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Scanner time recovered</v>
+      </c>
+      <c r="B6" t="str">
+        <v>28h 15m</v>
+      </c>
+      <c r="C6" t="str">
+        <v>duration</v>
+      </c>
+      <c r="D6" t="str">
+        <v>this month</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Travel-blocked candidates</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" t="str">
+        <v>count</v>
+      </c>
+      <c r="D7" t="str">
+        <v>auto-skipped by A* planner</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D7"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>location_id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>address</v>
+      </c>
+      <c r="D1" t="str">
+        <v>lat</v>
+      </c>
+      <c r="E1" t="str">
+        <v>lng</v>
+      </c>
+      <c r="F1" t="str">
+        <v>route_node_id</v>
+      </c>
+      <c r="G1" t="str">
+        <v>phone</v>
+      </c>
+      <c r="H1" t="str">
+        <v>arrival_buffer_minutes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>loc_innere_stadt</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Vienna Private Imaging — Innere Stadt</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Kärntner Straße 18, 1010 Wien</v>
+      </c>
+      <c r="D2">
+        <v>48.2082</v>
+      </c>
+      <c r="E2">
+        <v>16.3738</v>
+      </c>
+      <c r="F2" t="str">
+        <v>clinic_innere_stadt</v>
+      </c>
+      <c r="G2" t="str">
+        <v>+43 1 411 88 02</v>
+      </c>
+      <c r="H2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>loc_mariahilf</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Vienna Private Imaging — Mariahilf</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Mariahilfer Straße 88, 1070 Wien</v>
+      </c>
+      <c r="D3">
+        <v>48.1986</v>
+      </c>
+      <c r="E3">
+        <v>16.3478</v>
+      </c>
+      <c r="F3" t="str">
+        <v>clinic_mariahilf</v>
+      </c>
+      <c r="G3" t="str">
+        <v>+43 1 411 88 03</v>
+      </c>
+      <c r="H3">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>segment_id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>criteria</v>
+      </c>
+      <c r="D1" t="str">
+        <v>avg_acceptance</v>
+      </c>
+      <c r="E1" t="str">
+        <v>avg_pickup</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>seg_same_day</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Same-day opt-in</v>
+      </c>
+      <c r="C2" t="str">
+        <v>preferences.same_day = true AND earlier_opportunity_preference != none</v>
+      </c>
+      <c r="D2">
+        <v>0.83</v>
+      </c>
+      <c r="E2">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>seg_priority</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Priority customers</v>
+      </c>
+      <c r="C3" t="str">
+        <v>business_priority &gt;= 0.7</v>
+      </c>
+      <c r="D3">
+        <v>0.71</v>
+      </c>
+      <c r="E3">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>seg_referral_ready</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Referral-ready</v>
+      </c>
+      <c r="C4" t="str">
+        <v>eligibility.referral = true AND eligibility.safety_form = true</v>
+      </c>
+      <c r="D4">
+        <v>0.66</v>
+      </c>
+      <c r="E4">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>seg_close</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Lives within 30m travel</v>
+      </c>
+      <c r="C5" t="str">
+        <v>route.travel_minutes &lt;= 30</v>
+      </c>
+      <c r="D5">
+        <v>0.69</v>
+      </c>
+      <c r="E5">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>seg_demo</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Demo Çağan</v>
+      </c>
+      <c r="C6" t="str">
+        <v>customer_id = 'cust_cagan'</v>
+      </c>
+      <c r="D6">
+        <v>0.95</v>
+      </c>
+      <c r="E6">
+        <v>0.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C8"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>step</v>
+      </c>
+      <c r="B1" t="str">
+        <v>name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>description</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Hard filters</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Consent, eligibility, service, contrast, cooldown, opted out → boolean gates</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Route feasibility</v>
+      </c>
+      <c r="C3" t="str">
+        <v>travel + buffer ≤ time_left ⇒ feasible; else TRAVEL_BLOCKED</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Travel feasibility score</v>
+      </c>
+      <c r="C4" t="str">
+        <v>clamp((time_left − buffer − travel) / time_left, 0, 1)</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Weighted positives</v>
+      </c>
+      <c r="C5" t="str">
+        <v>0.30·eligibility + 0.20·urgency + 0.15·wait + 0.15·pickup + 0.10·business + 0.10·preference + 0.25·travel</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Cooldown penalty</v>
+      </c>
+      <c r="C6" t="str">
+        <v>− 0.20·cooldown</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Final score</v>
+      </c>
+      <c r="C7" t="str">
+        <v>100 × clamp(positives − penalty, 0, 1) — zero if blocked or travel-blocked</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Aggression</v>
+      </c>
+      <c r="C8" t="str">
+        <v>time_left → calm(1) / focused(2) / aggressive(5) / emergency(10) concurrent calls</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B12"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>sheet</v>
+      </c>
+      <c r="B1" t="str">
+        <v>supabase_table</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Customers</v>
+      </c>
+      <c r="B2" t="str">
+        <v>customers + customer_consents + customer_eligibility</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Slots</v>
+      </c>
+      <c r="B3" t="str">
+        <v>slots</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Waitlist</v>
+      </c>
+      <c r="B4" t="str">
+        <v>waitlist_entries</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Eligibility</v>
+      </c>
+      <c r="B5" t="str">
+        <v>customer_eligibility</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Calls</v>
+      </c>
+      <c r="B6" t="str">
+        <v>call_attempts</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Audit_Log</v>
+      </c>
+      <c r="B7" t="str">
+        <v>audit_log</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Rules</v>
+      </c>
+      <c r="B8" t="str">
+        <v>algorithm_rules</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Services</v>
+      </c>
+      <c r="B9" t="str">
+        <v>services</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Locations</v>
+      </c>
+      <c r="B10" t="str">
+        <v>locations</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Segments</v>
+      </c>
+      <c r="B11" t="str">
+        <v>(computed view, not stored)</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Scoring</v>
+      </c>
+      <c r="B12" t="str">
+        <v>(read-only reference)</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B12"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B6"/>
   <sheetData>
     <row r="1">
@@ -527,7 +967,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>Sync to Supabase</v>
+        <v>Sync to Supabase (or run in demo mode without Supabase)</v>
       </c>
     </row>
     <row r="6">
@@ -545,9 +985,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -556,6 +996,9 @@
       <c r="B1" t="str">
         <v>populates</v>
       </c>
+      <c r="C1" t="str">
+        <v>required</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -564,6 +1007,9 @@
       <c r="B2" t="str">
         <v>Slots</v>
       </c>
+      <c r="C2" t="str">
+        <v>Optional. Connect on /integrations.</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -572,6 +1018,9 @@
       <c r="B3" t="str">
         <v>Customers, Waitlist, Eligibility</v>
       </c>
+      <c r="C3" t="str">
+        <v>Recommended for bulk import.</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -580,17 +1029,31 @@
       <c r="B4" t="str">
         <v>Customers (single-row form on /customers)</v>
       </c>
+      <c r="C4" t="str">
+        <v>Always available.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Fonio webhooks</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Calls</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Required for real voice calling.</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y22"/>
+  <dimension ref="A1:AC23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -612,84 +1075,96 @@
         <v>requested_service</v>
       </c>
       <c r="G1" t="str">
+        <v>requested_body_part</v>
+      </c>
+      <c r="H1" t="str">
         <v>call_consent</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>sms_consent</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>voicemail_consent</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>recording_consent</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>safety_form_complete</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>referral_received</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>payment_ready</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>authorization_approved</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>contrast_status</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>home_postcode</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>home_lat</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>home_lng</v>
       </c>
-      <c r="S1" t="str">
+      <c r="T1" t="str">
         <v>booking_satisfaction</v>
       </c>
-      <c r="T1" t="str">
+      <c r="U1" t="str">
         <v>earlier_opportunity_preference</v>
       </c>
-      <c r="U1" t="str">
+      <c r="V1" t="str">
         <v>cascade_participation</v>
       </c>
-      <c r="V1" t="str">
+      <c r="W1" t="str">
         <v>business_priority</v>
       </c>
-      <c r="W1" t="str">
+      <c r="X1" t="str">
         <v>waiting_since</v>
       </c>
-      <c r="X1" t="str">
+      <c r="Y1" t="str">
+        <v>last_contacted_at</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>opted_out</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>notes</v>
+      </c>
+      <c r="AB1" t="str">
         <v>consent_source</v>
       </c>
-      <c r="Y1" t="str">
+      <c r="AC1" t="str">
         <v>consent_timestamp</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>cust_alex</v>
+        <v>cust_cagan</v>
       </c>
       <c r="B2" t="str">
-        <v>Alex Berger</v>
+        <v>Çağan Oflazoğlu</v>
       </c>
       <c r="C2" t="str">
-        <v>+43 1 478 21 04</v>
+        <v>+31 6 309 247 15</v>
       </c>
       <c r="D2" t="str">
-        <v>alex.berger@protonmail.com</v>
+        <v>cagan04oflazoglu@gmail.com</v>
       </c>
       <c r="E2" t="str">
-        <v>de</v>
+        <v>en</v>
       </c>
       <c r="F2" t="str">
         <v>MRI Knee</v>
       </c>
-      <c r="G2" t="b">
-        <v>1</v>
+      <c r="G2" t="str">
+        <v>Right knee</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -712,12 +1187,12 @@
       <c r="N2" t="b">
         <v>1</v>
       </c>
-      <c r="O2" t="str">
+      <c r="O2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P2" t="str">
         <v>not_required</v>
       </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
       <c r="Q2" t="str">
         <v/>
       </c>
@@ -725,39 +1200,51 @@
         <v/>
       </c>
       <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
         <v>urgently_wants_earlier</v>
       </c>
-      <c r="T2" t="str">
+      <c r="U2" t="str">
         <v>any_earlier</v>
       </c>
-      <c r="U2" t="str">
+      <c r="V2" t="str">
         <v>can_move</v>
       </c>
-      <c r="V2">
-        <v>0.7</v>
-      </c>
-      <c r="W2" t="str">
-        <v>2026-05-19T18:18:36.896Z</v>
+      <c r="W2">
+        <v>0.95</v>
       </c>
       <c r="X2" t="str">
+        <v>2026-06-05T22:34:25.011Z</v>
+      </c>
+      <c r="Y2" t="str">
+        <v/>
+      </c>
+      <c r="Z2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="str">
+        <v>Demo account — real Fonio calls land here. Lives near Innere Stadt.</v>
+      </c>
+      <c r="AB2" t="str">
         <v>import</v>
       </c>
-      <c r="Y2" t="str">
-        <v>2026-06-06T18:18:36.904Z</v>
+      <c r="AC2" t="str">
+        <v>2026-06-06T22:34:25.022Z</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>cust_sara</v>
+        <v>cust_alex</v>
       </c>
       <c r="B3" t="str">
-        <v>Sara Klein</v>
+        <v>Alex Berger</v>
       </c>
       <c r="C3" t="str">
-        <v>+43 1 366 88 17</v>
+        <v>+43 1 478 21 04</v>
       </c>
       <c r="D3" t="str">
-        <v>sara.klein@gmail.com</v>
+        <v>alex.berger@protonmail.com</v>
       </c>
       <c r="E3" t="str">
         <v>de</v>
@@ -765,8 +1252,8 @@
       <c r="F3" t="str">
         <v>MRI Knee</v>
       </c>
-      <c r="G3" t="b">
-        <v>1</v>
+      <c r="G3" t="str">
+        <v>Right knee</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -789,11 +1276,11 @@
       <c r="N3" t="b">
         <v>1</v>
       </c>
-      <c r="O3" t="str">
-        <v>cleared</v>
+      <c r="O3" t="b">
+        <v>1</v>
       </c>
       <c r="P3" t="str">
-        <v/>
+        <v>not_required</v>
       </c>
       <c r="Q3" t="str">
         <v/>
@@ -802,39 +1289,51 @@
         <v/>
       </c>
       <c r="S3" t="str">
-        <v>satisfied</v>
+        <v/>
       </c>
       <c r="T3" t="str">
-        <v>seven_days_earlier</v>
+        <v>urgently_wants_earlier</v>
       </c>
       <c r="U3" t="str">
+        <v>any_earlier</v>
+      </c>
+      <c r="V3" t="str">
         <v>can_move</v>
       </c>
-      <c r="V3">
-        <v>0.5</v>
-      </c>
-      <c r="W3" t="str">
-        <v>2026-05-26T18:18:36.896Z</v>
+      <c r="W3">
+        <v>0.7</v>
       </c>
       <c r="X3" t="str">
+        <v>2026-05-19T22:34:25.011Z</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>2026-05-29T22:34:25.011Z</v>
+      </c>
+      <c r="Z3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="str">
+        <v/>
+      </c>
+      <c r="AB3" t="str">
         <v>import</v>
       </c>
-      <c r="Y3" t="str">
-        <v>2026-06-06T18:18:36.904Z</v>
+      <c r="AC3" t="str">
+        <v>2026-06-06T22:34:25.023Z</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>cust_jonas</v>
+        <v>cust_sara</v>
       </c>
       <c r="B4" t="str">
-        <v>Jonas Weber</v>
+        <v>Sara Klein</v>
       </c>
       <c r="C4" t="str">
-        <v>+43 660 412 09 88</v>
+        <v>+43 1 366 88 17</v>
       </c>
       <c r="D4" t="str">
-        <v>jonas.weber@outlook.com</v>
+        <v>sara.klein@gmail.com</v>
       </c>
       <c r="E4" t="str">
         <v>de</v>
@@ -842,14 +1341,14 @@
       <c r="F4" t="str">
         <v>MRI Knee</v>
       </c>
-      <c r="G4" t="b">
-        <v>1</v>
+      <c r="G4" t="str">
+        <v>Left knee</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
       </c>
       <c r="I4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -866,11 +1365,11 @@
       <c r="N4" t="b">
         <v>1</v>
       </c>
-      <c r="O4" t="str">
-        <v>not_required</v>
+      <c r="O4" t="b">
+        <v>1</v>
       </c>
       <c r="P4" t="str">
-        <v/>
+        <v>cleared</v>
       </c>
       <c r="Q4" t="str">
         <v/>
@@ -879,48 +1378,60 @@
         <v/>
       </c>
       <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
         <v>satisfied</v>
       </c>
-      <c r="T4" t="str">
-        <v>none</v>
-      </c>
       <c r="U4" t="str">
-        <v>do_not_move</v>
-      </c>
-      <c r="V4">
-        <v>0.4</v>
-      </c>
-      <c r="W4" t="str">
-        <v>2026-05-15T18:18:36.896Z</v>
+        <v>seven_days_earlier</v>
+      </c>
+      <c r="V4" t="str">
+        <v>can_move</v>
+      </c>
+      <c r="W4">
+        <v>0.5</v>
       </c>
       <c r="X4" t="str">
+        <v>2026-05-26T22:34:25.011Z</v>
+      </c>
+      <c r="Y4" t="str">
+        <v/>
+      </c>
+      <c r="Z4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="str">
+        <v/>
+      </c>
+      <c r="AB4" t="str">
         <v>import</v>
       </c>
-      <c r="Y4" t="str">
-        <v>2026-06-06T18:18:36.904Z</v>
+      <c r="AC4" t="str">
+        <v>2026-06-06T22:34:25.023Z</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>cust_mia</v>
+        <v>cust_jonas</v>
       </c>
       <c r="B5" t="str">
-        <v>Mia Novak</v>
+        <v>Jonas Weber</v>
       </c>
       <c r="C5" t="str">
-        <v>+43 676 224 18 53</v>
+        <v>+43 660 412 09 88</v>
       </c>
       <c r="D5" t="str">
-        <v>mia.novak@kabsi.at</v>
+        <v>jonas.weber@outlook.com</v>
       </c>
       <c r="E5" t="str">
-        <v>en</v>
+        <v>de</v>
       </c>
       <c r="F5" t="str">
         <v>MRI Knee</v>
       </c>
-      <c r="G5" t="b">
-        <v>1</v>
+      <c r="G5" t="str">
+        <v/>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -929,7 +1440,7 @@
         <v>1</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
@@ -943,12 +1454,12 @@
       <c r="N5" t="b">
         <v>1</v>
       </c>
-      <c r="O5" t="str">
+      <c r="O5" t="b">
+        <v>1</v>
+      </c>
+      <c r="P5" t="str">
         <v>not_required</v>
       </c>
-      <c r="P5" t="str">
-        <v/>
-      </c>
       <c r="Q5" t="str">
         <v/>
       </c>
@@ -956,51 +1467,63 @@
         <v/>
       </c>
       <c r="S5" t="str">
-        <v>neutral</v>
+        <v/>
       </c>
       <c r="T5" t="str">
-        <v>any_earlier</v>
+        <v>satisfied</v>
       </c>
       <c r="U5" t="str">
-        <v>can_move</v>
-      </c>
-      <c r="V5">
-        <v>0.6</v>
-      </c>
-      <c r="W5" t="str">
-        <v>2026-05-23T18:18:36.896Z</v>
+        <v>none</v>
+      </c>
+      <c r="V5" t="str">
+        <v>do_not_move</v>
+      </c>
+      <c r="W5">
+        <v>0.4</v>
       </c>
       <c r="X5" t="str">
+        <v>2026-05-15T22:34:25.011Z</v>
+      </c>
+      <c r="Y5" t="str">
+        <v/>
+      </c>
+      <c r="Z5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="str">
+        <v/>
+      </c>
+      <c r="AB5" t="str">
         <v>import</v>
       </c>
-      <c r="Y5" t="str">
-        <v>2026-06-06T18:18:36.904Z</v>
+      <c r="AC5" t="str">
+        <v>2026-06-06T22:34:25.023Z</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>cust_omar</v>
+        <v>cust_mia</v>
       </c>
       <c r="B6" t="str">
-        <v>Omar Demir</v>
+        <v>Mia Novak</v>
       </c>
       <c r="C6" t="str">
-        <v>+43 660 933 41 27</v>
+        <v>+43 676 224 18 53</v>
       </c>
       <c r="D6" t="str">
-        <v>omar.demir@gmx.at</v>
+        <v>mia.novak@kabsi.at</v>
       </c>
       <c r="E6" t="str">
-        <v>tr</v>
+        <v>en</v>
       </c>
       <c r="F6" t="str">
         <v>MRI Knee</v>
       </c>
-      <c r="G6" t="b">
-        <v>1</v>
+      <c r="G6" t="str">
+        <v>Left knee</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -1018,13 +1541,13 @@
         <v>1</v>
       </c>
       <c r="N6" t="b">
-        <v>0</v>
-      </c>
-      <c r="O6" t="str">
-        <v>pending</v>
+        <v>1</v>
+      </c>
+      <c r="O6" t="b">
+        <v>1</v>
       </c>
       <c r="P6" t="str">
-        <v/>
+        <v>not_required</v>
       </c>
       <c r="Q6" t="str">
         <v/>
@@ -1033,54 +1556,66 @@
         <v/>
       </c>
       <c r="S6" t="str">
-        <v>dissatisfied</v>
+        <v/>
       </c>
       <c r="T6" t="str">
+        <v>neutral</v>
+      </c>
+      <c r="U6" t="str">
         <v>any_earlier</v>
       </c>
-      <c r="U6" t="str">
+      <c r="V6" t="str">
         <v>can_move</v>
       </c>
-      <c r="V6">
-        <v>0.55</v>
-      </c>
-      <c r="W6" t="str">
-        <v>2026-05-28T18:18:36.896Z</v>
+      <c r="W6">
+        <v>0.6</v>
       </c>
       <c r="X6" t="str">
+        <v>2026-05-23T22:34:25.011Z</v>
+      </c>
+      <c r="Y6" t="str">
+        <v/>
+      </c>
+      <c r="Z6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="str">
+        <v/>
+      </c>
+      <c r="AB6" t="str">
         <v>import</v>
       </c>
-      <c r="Y6" t="str">
-        <v>2026-06-06T18:18:36.904Z</v>
+      <c r="AC6" t="str">
+        <v>2026-06-06T22:34:25.023Z</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>cust_lena</v>
+        <v>cust_omar</v>
       </c>
       <c r="B7" t="str">
-        <v>Lena Brunner</v>
+        <v>Omar Demir</v>
       </c>
       <c r="C7" t="str">
-        <v>+43 1 712 04 92</v>
+        <v>+43 660 933 41 27</v>
       </c>
       <c r="D7" t="str">
-        <v>lena.brunner@inode.at</v>
+        <v>omar.demir@gmx.at</v>
       </c>
       <c r="E7" t="str">
-        <v>de</v>
+        <v>tr</v>
       </c>
       <c r="F7" t="str">
         <v>MRI Knee</v>
       </c>
-      <c r="G7" t="b">
-        <v>1</v>
+      <c r="G7" t="str">
+        <v/>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
@@ -1097,11 +1632,11 @@
       <c r="N7" t="b">
         <v>1</v>
       </c>
-      <c r="O7" t="str">
-        <v>not_required</v>
+      <c r="O7" t="b">
+        <v>0</v>
       </c>
       <c r="P7" t="str">
-        <v/>
+        <v>pending</v>
       </c>
       <c r="Q7" t="str">
         <v/>
@@ -1110,48 +1645,60 @@
         <v/>
       </c>
       <c r="S7" t="str">
-        <v>neutral</v>
+        <v/>
       </c>
       <c r="T7" t="str">
-        <v>none</v>
+        <v>dissatisfied</v>
       </c>
       <c r="U7" t="str">
-        <v>manual_approval</v>
-      </c>
-      <c r="V7">
-        <v>0.4</v>
-      </c>
-      <c r="W7" t="str">
-        <v/>
+        <v>any_earlier</v>
+      </c>
+      <c r="V7" t="str">
+        <v>can_move</v>
+      </c>
+      <c r="W7">
+        <v>0.55</v>
       </c>
       <c r="X7" t="str">
+        <v>2026-05-28T22:34:25.011Z</v>
+      </c>
+      <c r="Y7" t="str">
+        <v/>
+      </c>
+      <c r="Z7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="str">
+        <v/>
+      </c>
+      <c r="AB7" t="str">
         <v>import</v>
       </c>
-      <c r="Y7" t="str">
-        <v>2026-06-06T18:18:36.904Z</v>
+      <c r="AC7" t="str">
+        <v>2026-06-06T22:34:25.023Z</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>cust_helena</v>
+        <v>cust_lena</v>
       </c>
       <c r="B8" t="str">
-        <v>Helena Vogel</v>
+        <v>Lena Brunner</v>
       </c>
       <c r="C8" t="str">
-        <v>+43 699 184 22 31</v>
+        <v>+43 1 712 04 92</v>
       </c>
       <c r="D8" t="str">
-        <v>helena.vogel@a1.net</v>
+        <v>lena.brunner@inode.at</v>
       </c>
       <c r="E8" t="str">
         <v>de</v>
       </c>
       <c r="F8" t="str">
-        <v>MRI Brain</v>
-      </c>
-      <c r="G8" t="b">
-        <v>1</v>
+        <v>MRI Knee</v>
+      </c>
+      <c r="G8" t="str">
+        <v/>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -1174,12 +1721,12 @@
       <c r="N8" t="b">
         <v>1</v>
       </c>
-      <c r="O8" t="str">
+      <c r="O8" t="b">
+        <v>1</v>
+      </c>
+      <c r="P8" t="str">
         <v>not_required</v>
       </c>
-      <c r="P8" t="str">
-        <v/>
-      </c>
       <c r="Q8" t="str">
         <v/>
       </c>
@@ -1187,48 +1734,60 @@
         <v/>
       </c>
       <c r="S8" t="str">
-        <v>dissatisfied</v>
+        <v/>
       </c>
       <c r="T8" t="str">
-        <v>any_earlier</v>
+        <v>neutral</v>
       </c>
       <c r="U8" t="str">
-        <v>can_move</v>
-      </c>
-      <c r="V8">
-        <v>0.65</v>
-      </c>
-      <c r="W8" t="str">
-        <v>2026-05-16T18:18:36.896Z</v>
+        <v>none</v>
+      </c>
+      <c r="V8" t="str">
+        <v>manual_approval</v>
+      </c>
+      <c r="W8">
+        <v>0.4</v>
       </c>
       <c r="X8" t="str">
+        <v/>
+      </c>
+      <c r="Y8" t="str">
+        <v/>
+      </c>
+      <c r="Z8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="str">
+        <v/>
+      </c>
+      <c r="AB8" t="str">
         <v>import</v>
       </c>
-      <c r="Y8" t="str">
-        <v>2026-06-06T18:18:36.904Z</v>
+      <c r="AC8" t="str">
+        <v>2026-06-06T22:34:25.023Z</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>cust_kerem</v>
+        <v>cust_helena</v>
       </c>
       <c r="B9" t="str">
-        <v>Kerem Yıldız</v>
+        <v>Helena Vogel</v>
       </c>
       <c r="C9" t="str">
-        <v>+43 660 728 03 14</v>
+        <v>+43 699 184 22 31</v>
       </c>
       <c r="D9" t="str">
-        <v>kerem.yildiz@yandex.com</v>
+        <v>helena.vogel@a1.net</v>
       </c>
       <c r="E9" t="str">
-        <v>tr</v>
+        <v>de</v>
       </c>
       <c r="F9" t="str">
-        <v>CT Chest</v>
-      </c>
-      <c r="G9" t="b">
-        <v>1</v>
+        <v>MRI Brain</v>
+      </c>
+      <c r="G9" t="str">
+        <v/>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -1240,7 +1799,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
@@ -1251,12 +1810,12 @@
       <c r="N9" t="b">
         <v>1</v>
       </c>
-      <c r="O9" t="str">
+      <c r="O9" t="b">
+        <v>1</v>
+      </c>
+      <c r="P9" t="str">
         <v>not_required</v>
       </c>
-      <c r="P9" t="str">
-        <v/>
-      </c>
       <c r="Q9" t="str">
         <v/>
       </c>
@@ -1264,48 +1823,60 @@
         <v/>
       </c>
       <c r="S9" t="str">
-        <v>neutral</v>
+        <v/>
       </c>
       <c r="T9" t="str">
-        <v>seven_days_earlier</v>
+        <v>dissatisfied</v>
       </c>
       <c r="U9" t="str">
+        <v>any_earlier</v>
+      </c>
+      <c r="V9" t="str">
         <v>can_move</v>
       </c>
-      <c r="V9">
-        <v>0.5</v>
-      </c>
-      <c r="W9" t="str">
-        <v>2026-05-30T18:18:36.896Z</v>
+      <c r="W9">
+        <v>0.65</v>
       </c>
       <c r="X9" t="str">
+        <v>2026-05-16T22:34:25.011Z</v>
+      </c>
+      <c r="Y9" t="str">
+        <v/>
+      </c>
+      <c r="Z9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="str">
+        <v/>
+      </c>
+      <c r="AB9" t="str">
         <v>import</v>
       </c>
-      <c r="Y9" t="str">
-        <v>2026-06-06T18:18:36.904Z</v>
+      <c r="AC9" t="str">
+        <v>2026-06-06T22:34:25.023Z</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>cust_isabella</v>
+        <v>cust_kerem</v>
       </c>
       <c r="B10" t="str">
-        <v>Isabella Moretti</v>
+        <v>Kerem Yıldız</v>
       </c>
       <c r="C10" t="str">
-        <v>+43 676 411 87 02</v>
+        <v>+43 660 728 03 14</v>
       </c>
       <c r="D10" t="str">
-        <v>isabella.moretti@chello.at</v>
+        <v>kerem.yildiz@yandex.com</v>
       </c>
       <c r="E10" t="str">
-        <v>en</v>
+        <v>tr</v>
       </c>
       <c r="F10" t="str">
-        <v>MRI Spine</v>
-      </c>
-      <c r="G10" t="b">
-        <v>1</v>
+        <v>CT Chest</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -1320,20 +1891,20 @@
         <v>1</v>
       </c>
       <c r="L10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
       </c>
-      <c r="O10" t="str">
+      <c r="O10" t="b">
+        <v>1</v>
+      </c>
+      <c r="P10" t="str">
         <v>not_required</v>
       </c>
-      <c r="P10" t="str">
-        <v/>
-      </c>
       <c r="Q10" t="str">
         <v/>
       </c>
@@ -1341,57 +1912,69 @@
         <v/>
       </c>
       <c r="S10" t="str">
+        <v/>
+      </c>
+      <c r="T10" t="str">
         <v>neutral</v>
       </c>
-      <c r="T10" t="str">
-        <v>any_earlier</v>
-      </c>
       <c r="U10" t="str">
+        <v>seven_days_earlier</v>
+      </c>
+      <c r="V10" t="str">
         <v>can_move</v>
       </c>
-      <c r="V10">
-        <v>0.6</v>
-      </c>
-      <c r="W10" t="str">
-        <v>2026-05-21T18:18:36.896Z</v>
+      <c r="W10">
+        <v>0.5</v>
       </c>
       <c r="X10" t="str">
+        <v>2026-05-30T22:34:25.011Z</v>
+      </c>
+      <c r="Y10" t="str">
+        <v/>
+      </c>
+      <c r="Z10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="str">
+        <v/>
+      </c>
+      <c r="AB10" t="str">
         <v>import</v>
       </c>
-      <c r="Y10" t="str">
-        <v>2026-06-06T18:18:36.904Z</v>
+      <c r="AC10" t="str">
+        <v>2026-06-06T22:34:25.023Z</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>cust_lukas</v>
+        <v>cust_isabella</v>
       </c>
       <c r="B11" t="str">
-        <v>Lukas Hofer</v>
+        <v>Isabella Moretti</v>
       </c>
       <c r="C11" t="str">
-        <v>+43 660 184 33 09</v>
+        <v>+43 676 411 87 02</v>
       </c>
       <c r="D11" t="str">
-        <v>lukas.hofer@protonmail.com</v>
+        <v>isabella.moretti@chello.at</v>
       </c>
       <c r="E11" t="str">
-        <v>de</v>
+        <v>en</v>
       </c>
       <c r="F11" t="str">
-        <v>MRI Knee</v>
-      </c>
-      <c r="G11" t="b">
-        <v>0</v>
+        <v>MRI Spine</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
@@ -1403,14 +1986,14 @@
         <v>1</v>
       </c>
       <c r="N11" t="b">
-        <v>1</v>
-      </c>
-      <c r="O11" t="str">
+        <v>0</v>
+      </c>
+      <c r="O11" t="b">
+        <v>1</v>
+      </c>
+      <c r="P11" t="str">
         <v>not_required</v>
       </c>
-      <c r="P11" t="str">
-        <v/>
-      </c>
       <c r="Q11" t="str">
         <v/>
       </c>
@@ -1418,60 +2001,72 @@
         <v/>
       </c>
       <c r="S11" t="str">
+        <v/>
+      </c>
+      <c r="T11" t="str">
         <v>neutral</v>
       </c>
-      <c r="T11" t="str">
+      <c r="U11" t="str">
         <v>any_earlier</v>
       </c>
-      <c r="U11" t="str">
+      <c r="V11" t="str">
         <v>can_move</v>
       </c>
-      <c r="V11">
-        <v>0.5</v>
-      </c>
-      <c r="W11" t="str">
-        <v>2026-05-24T18:18:36.896Z</v>
+      <c r="W11">
+        <v>0.6</v>
       </c>
       <c r="X11" t="str">
+        <v>2026-05-21T22:34:25.011Z</v>
+      </c>
+      <c r="Y11" t="str">
+        <v/>
+      </c>
+      <c r="Z11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="str">
+        <v/>
+      </c>
+      <c r="AB11" t="str">
         <v>import</v>
       </c>
-      <c r="Y11" t="str">
-        <v>2026-06-06T18:18:36.904Z</v>
+      <c r="AC11" t="str">
+        <v>2026-06-06T22:34:25.023Z</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>cust_clara</v>
+        <v>cust_lukas</v>
       </c>
       <c r="B12" t="str">
-        <v>Clara Pichler</v>
+        <v>Lukas Hofer</v>
       </c>
       <c r="C12" t="str">
-        <v>+43 699 902 16 41</v>
+        <v>+43 660 184 33 09</v>
       </c>
       <c r="D12" t="str">
-        <v>clara.pichler@gmail.com</v>
+        <v>lukas.hofer@protonmail.com</v>
       </c>
       <c r="E12" t="str">
         <v>de</v>
       </c>
       <c r="F12" t="str">
-        <v>CT Abdomen</v>
-      </c>
-      <c r="G12" t="b">
-        <v>1</v>
+        <v>MRI Knee</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
       </c>
       <c r="H12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="b">
         <v>1</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
@@ -1482,11 +2077,11 @@
       <c r="N12" t="b">
         <v>1</v>
       </c>
-      <c r="O12" t="str">
-        <v>cleared</v>
+      <c r="O12" t="b">
+        <v>1</v>
       </c>
       <c r="P12" t="str">
-        <v/>
+        <v>not_required</v>
       </c>
       <c r="Q12" t="str">
         <v/>
@@ -1495,48 +2090,60 @@
         <v/>
       </c>
       <c r="S12" t="str">
-        <v>urgently_wants_earlier</v>
+        <v/>
       </c>
       <c r="T12" t="str">
-        <v>same_day</v>
+        <v>neutral</v>
       </c>
       <c r="U12" t="str">
+        <v>any_earlier</v>
+      </c>
+      <c r="V12" t="str">
         <v>can_move</v>
       </c>
-      <c r="V12">
-        <v>0.72</v>
-      </c>
-      <c r="W12" t="str">
-        <v>2026-06-01T18:18:36.896Z</v>
+      <c r="W12">
+        <v>0.5</v>
       </c>
       <c r="X12" t="str">
+        <v>2026-05-24T22:34:25.011Z</v>
+      </c>
+      <c r="Y12" t="str">
+        <v/>
+      </c>
+      <c r="Z12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="str">
+        <v/>
+      </c>
+      <c r="AB12" t="str">
         <v>import</v>
       </c>
-      <c r="Y12" t="str">
-        <v>2026-06-06T18:18:36.904Z</v>
+      <c r="AC12" t="str">
+        <v>2026-06-06T22:34:25.023Z</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>cust_paul</v>
+        <v>cust_clara</v>
       </c>
       <c r="B13" t="str">
-        <v>Paul Kovač</v>
+        <v>Clara Pichler</v>
       </c>
       <c r="C13" t="str">
-        <v>+43 660 552 18 77</v>
+        <v>+43 699 902 16 41</v>
       </c>
       <c r="D13" t="str">
-        <v>paul.kovac@aon.at</v>
+        <v>clara.pichler@gmail.com</v>
       </c>
       <c r="E13" t="str">
-        <v>en</v>
+        <v>de</v>
       </c>
       <c r="F13" t="str">
-        <v>MRI Spine</v>
-      </c>
-      <c r="G13" t="b">
-        <v>1</v>
+        <v>CT Abdomen</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -1559,11 +2166,11 @@
       <c r="N13" t="b">
         <v>1</v>
       </c>
-      <c r="O13" t="str">
-        <v>not_required</v>
+      <c r="O13" t="b">
+        <v>1</v>
       </c>
       <c r="P13" t="str">
-        <v/>
+        <v>cleared</v>
       </c>
       <c r="Q13" t="str">
         <v/>
@@ -1572,48 +2179,60 @@
         <v/>
       </c>
       <c r="S13" t="str">
-        <v>neutral</v>
+        <v/>
       </c>
       <c r="T13" t="str">
-        <v>seven_days_earlier</v>
+        <v>urgently_wants_earlier</v>
       </c>
       <c r="U13" t="str">
-        <v>move_once</v>
-      </c>
-      <c r="V13">
-        <v>0.55</v>
-      </c>
-      <c r="W13" t="str">
-        <v>2026-05-18T18:18:36.896Z</v>
+        <v>same_day</v>
+      </c>
+      <c r="V13" t="str">
+        <v>can_move</v>
+      </c>
+      <c r="W13">
+        <v>0.72</v>
       </c>
       <c r="X13" t="str">
+        <v>2026-06-01T22:34:25.011Z</v>
+      </c>
+      <c r="Y13" t="str">
+        <v/>
+      </c>
+      <c r="Z13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="str">
+        <v/>
+      </c>
+      <c r="AB13" t="str">
         <v>import</v>
       </c>
-      <c r="Y13" t="str">
-        <v>2026-06-06T18:18:36.904Z</v>
+      <c r="AC13" t="str">
+        <v>2026-06-06T22:34:25.023Z</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>cust_emma</v>
+        <v>cust_paul</v>
       </c>
       <c r="B14" t="str">
-        <v>Emma Schreiner</v>
+        <v>Paul Kovač</v>
       </c>
       <c r="C14" t="str">
-        <v>+43 676 901 23 42</v>
+        <v>+43 660 552 18 77</v>
       </c>
       <c r="D14" t="str">
-        <v>emma.schreiner@gmx.at</v>
+        <v>paul.kovac@aon.at</v>
       </c>
       <c r="E14" t="str">
-        <v>de</v>
+        <v>en</v>
       </c>
       <c r="F14" t="str">
-        <v>Ultrasound</v>
-      </c>
-      <c r="G14" t="b">
-        <v>1</v>
+        <v>MRI Spine</v>
+      </c>
+      <c r="G14" t="str">
+        <v/>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -1636,12 +2255,12 @@
       <c r="N14" t="b">
         <v>1</v>
       </c>
-      <c r="O14" t="str">
+      <c r="O14" t="b">
+        <v>1</v>
+      </c>
+      <c r="P14" t="str">
         <v>not_required</v>
       </c>
-      <c r="P14" t="str">
-        <v/>
-      </c>
       <c r="Q14" t="str">
         <v/>
       </c>
@@ -1649,48 +2268,60 @@
         <v/>
       </c>
       <c r="S14" t="str">
+        <v/>
+      </c>
+      <c r="T14" t="str">
         <v>neutral</v>
       </c>
-      <c r="T14" t="str">
-        <v>any_earlier</v>
-      </c>
       <c r="U14" t="str">
-        <v>can_move</v>
-      </c>
-      <c r="V14">
-        <v>0.45</v>
-      </c>
-      <c r="W14" t="str">
-        <v>2026-06-02T18:18:36.896Z</v>
+        <v>seven_days_earlier</v>
+      </c>
+      <c r="V14" t="str">
+        <v>move_once</v>
+      </c>
+      <c r="W14">
+        <v>0.55</v>
       </c>
       <c r="X14" t="str">
+        <v>2026-05-18T22:34:25.011Z</v>
+      </c>
+      <c r="Y14" t="str">
+        <v/>
+      </c>
+      <c r="Z14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="str">
+        <v/>
+      </c>
+      <c r="AB14" t="str">
         <v>import</v>
       </c>
-      <c r="Y14" t="str">
-        <v>2026-06-06T18:18:36.904Z</v>
+      <c r="AC14" t="str">
+        <v>2026-06-06T22:34:25.023Z</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>cust_finn</v>
+        <v>cust_emma</v>
       </c>
       <c r="B15" t="str">
-        <v>Finn Rauch</v>
+        <v>Emma Schreiner</v>
       </c>
       <c r="C15" t="str">
-        <v>+43 660 220 41 88</v>
+        <v>+43 676 901 23 42</v>
       </c>
       <c r="D15" t="str">
-        <v>finn.rauch@chello.at</v>
+        <v>emma.schreiner@gmx.at</v>
       </c>
       <c r="E15" t="str">
         <v>de</v>
       </c>
       <c r="F15" t="str">
-        <v>MRI Brain</v>
-      </c>
-      <c r="G15" t="b">
-        <v>1</v>
+        <v>Ultrasound</v>
+      </c>
+      <c r="G15" t="str">
+        <v/>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -1705,7 +2336,7 @@
         <v>1</v>
       </c>
       <c r="L15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="b">
         <v>1</v>
@@ -1713,12 +2344,12 @@
       <c r="N15" t="b">
         <v>1</v>
       </c>
-      <c r="O15" t="str">
+      <c r="O15" t="b">
+        <v>1</v>
+      </c>
+      <c r="P15" t="str">
         <v>not_required</v>
       </c>
-      <c r="P15" t="str">
-        <v/>
-      </c>
       <c r="Q15" t="str">
         <v/>
       </c>
@@ -1726,48 +2357,60 @@
         <v/>
       </c>
       <c r="S15" t="str">
-        <v>dissatisfied</v>
+        <v/>
       </c>
       <c r="T15" t="str">
+        <v>neutral</v>
+      </c>
+      <c r="U15" t="str">
         <v>any_earlier</v>
       </c>
-      <c r="U15" t="str">
+      <c r="V15" t="str">
         <v>can_move</v>
       </c>
-      <c r="V15">
-        <v>0.6</v>
-      </c>
-      <c r="W15" t="str">
-        <v>2026-05-29T18:18:36.896Z</v>
+      <c r="W15">
+        <v>0.45</v>
       </c>
       <c r="X15" t="str">
+        <v>2026-06-02T22:34:25.011Z</v>
+      </c>
+      <c r="Y15" t="str">
+        <v/>
+      </c>
+      <c r="Z15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="str">
+        <v/>
+      </c>
+      <c r="AB15" t="str">
         <v>import</v>
       </c>
-      <c r="Y15" t="str">
-        <v>2026-06-06T18:18:36.904Z</v>
+      <c r="AC15" t="str">
+        <v>2026-06-06T22:34:25.023Z</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>cust_zeynep</v>
+        <v>cust_finn</v>
       </c>
       <c r="B16" t="str">
-        <v>Zeynep Aslan</v>
+        <v>Finn Rauch</v>
       </c>
       <c r="C16" t="str">
-        <v>+43 676 802 14 27</v>
+        <v>+43 660 220 41 88</v>
       </c>
       <c r="D16" t="str">
-        <v>zeynep.aslan@gmail.com</v>
+        <v>finn.rauch@chello.at</v>
       </c>
       <c r="E16" t="str">
-        <v>tr</v>
+        <v>de</v>
       </c>
       <c r="F16" t="str">
-        <v>MRI Knee</v>
-      </c>
-      <c r="G16" t="b">
-        <v>1</v>
+        <v>MRI Brain</v>
+      </c>
+      <c r="G16" t="str">
+        <v/>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -1785,17 +2428,17 @@
         <v>1</v>
       </c>
       <c r="M16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
       </c>
-      <c r="O16" t="str">
+      <c r="O16" t="b">
+        <v>1</v>
+      </c>
+      <c r="P16" t="str">
         <v>not_required</v>
       </c>
-      <c r="P16" t="str">
-        <v/>
-      </c>
       <c r="Q16" t="str">
         <v/>
       </c>
@@ -1803,54 +2446,66 @@
         <v/>
       </c>
       <c r="S16" t="str">
-        <v>urgently_wants_earlier</v>
+        <v/>
       </c>
       <c r="T16" t="str">
+        <v>dissatisfied</v>
+      </c>
+      <c r="U16" t="str">
         <v>any_earlier</v>
       </c>
-      <c r="U16" t="str">
+      <c r="V16" t="str">
         <v>can_move</v>
       </c>
-      <c r="V16">
-        <v>0.68</v>
-      </c>
-      <c r="W16" t="str">
-        <v>2026-06-04T18:18:36.896Z</v>
+      <c r="W16">
+        <v>0.6</v>
       </c>
       <c r="X16" t="str">
+        <v>2026-05-29T22:34:25.011Z</v>
+      </c>
+      <c r="Y16" t="str">
+        <v/>
+      </c>
+      <c r="Z16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="str">
+        <v/>
+      </c>
+      <c r="AB16" t="str">
         <v>import</v>
       </c>
-      <c r="Y16" t="str">
-        <v>2026-06-06T18:18:36.904Z</v>
+      <c r="AC16" t="str">
+        <v>2026-06-06T22:34:25.023Z</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>cust_david</v>
+        <v>cust_zeynep</v>
       </c>
       <c r="B17" t="str">
-        <v>David Marković</v>
+        <v>Zeynep Aslan</v>
       </c>
       <c r="C17" t="str">
-        <v>+43 660 733 92 41</v>
+        <v>+43 676 802 14 27</v>
       </c>
       <c r="D17" t="str">
-        <v>david.markovic@protonmail.com</v>
+        <v>zeynep.aslan@gmail.com</v>
       </c>
       <c r="E17" t="str">
-        <v>en</v>
+        <v>tr</v>
       </c>
       <c r="F17" t="str">
-        <v>X-ray</v>
-      </c>
-      <c r="G17" t="b">
-        <v>1</v>
+        <v>MRI Knee</v>
+      </c>
+      <c r="G17" t="str">
+        <v/>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
@@ -1867,12 +2522,12 @@
       <c r="N17" t="b">
         <v>1</v>
       </c>
-      <c r="O17" t="str">
+      <c r="O17" t="b">
+        <v>1</v>
+      </c>
+      <c r="P17" t="str">
         <v>not_required</v>
       </c>
-      <c r="P17" t="str">
-        <v/>
-      </c>
       <c r="Q17" t="str">
         <v/>
       </c>
@@ -1880,48 +2535,60 @@
         <v/>
       </c>
       <c r="S17" t="str">
-        <v>neutral</v>
+        <v/>
       </c>
       <c r="T17" t="str">
-        <v>none</v>
+        <v>urgently_wants_earlier</v>
       </c>
       <c r="U17" t="str">
+        <v>any_earlier</v>
+      </c>
+      <c r="V17" t="str">
         <v>can_move</v>
       </c>
-      <c r="V17">
-        <v>0.4</v>
-      </c>
-      <c r="W17" t="str">
-        <v/>
+      <c r="W17">
+        <v>0.68</v>
       </c>
       <c r="X17" t="str">
+        <v>2026-06-04T22:34:25.011Z</v>
+      </c>
+      <c r="Y17" t="str">
+        <v/>
+      </c>
+      <c r="Z17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="str">
+        <v/>
+      </c>
+      <c r="AB17" t="str">
         <v>import</v>
       </c>
-      <c r="Y17" t="str">
-        <v>2026-06-06T18:18:36.904Z</v>
+      <c r="AC17" t="str">
+        <v>2026-06-06T22:34:25.023Z</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>cust_anna</v>
+        <v>cust_david</v>
       </c>
       <c r="B18" t="str">
-        <v>Anna Greiner</v>
+        <v>David Marković</v>
       </c>
       <c r="C18" t="str">
-        <v>+43 699 411 23 80</v>
+        <v>+43 660 733 92 41</v>
       </c>
       <c r="D18" t="str">
-        <v>anna.greiner@a1.net</v>
+        <v>david.markovic@protonmail.com</v>
       </c>
       <c r="E18" t="str">
-        <v>de</v>
+        <v>en</v>
       </c>
       <c r="F18" t="str">
-        <v>MRI Brain</v>
-      </c>
-      <c r="G18" t="b">
-        <v>1</v>
+        <v>X-ray</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -1930,7 +2597,7 @@
         <v>1</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
@@ -1944,12 +2611,12 @@
       <c r="N18" t="b">
         <v>1</v>
       </c>
-      <c r="O18" t="str">
+      <c r="O18" t="b">
+        <v>1</v>
+      </c>
+      <c r="P18" t="str">
         <v>not_required</v>
       </c>
-      <c r="P18" t="str">
-        <v/>
-      </c>
       <c r="Q18" t="str">
         <v/>
       </c>
@@ -1957,48 +2624,60 @@
         <v/>
       </c>
       <c r="S18" t="str">
+        <v/>
+      </c>
+      <c r="T18" t="str">
         <v>neutral</v>
       </c>
-      <c r="T18" t="str">
-        <v>seven_days_earlier</v>
-      </c>
       <c r="U18" t="str">
+        <v>none</v>
+      </c>
+      <c r="V18" t="str">
         <v>can_move</v>
       </c>
-      <c r="V18">
-        <v>0.5</v>
-      </c>
-      <c r="W18" t="str">
-        <v>2026-05-25T18:18:36.896Z</v>
+      <c r="W18">
+        <v>0.4</v>
       </c>
       <c r="X18" t="str">
+        <v/>
+      </c>
+      <c r="Y18" t="str">
+        <v/>
+      </c>
+      <c r="Z18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="str">
+        <v/>
+      </c>
+      <c r="AB18" t="str">
         <v>import</v>
       </c>
-      <c r="Y18" t="str">
-        <v>2026-06-06T18:18:36.904Z</v>
+      <c r="AC18" t="str">
+        <v>2026-06-06T22:34:25.023Z</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>cust_tobias</v>
+        <v>cust_anna</v>
       </c>
       <c r="B19" t="str">
-        <v>Tobias Ehrlich</v>
+        <v>Anna Greiner</v>
       </c>
       <c r="C19" t="str">
-        <v>+43 660 411 92 33</v>
+        <v>+43 699 411 23 80</v>
       </c>
       <c r="D19" t="str">
-        <v>tobias.ehrlich@gmx.at</v>
+        <v>anna.greiner@a1.net</v>
       </c>
       <c r="E19" t="str">
         <v>de</v>
       </c>
       <c r="F19" t="str">
-        <v>CT Chest</v>
-      </c>
-      <c r="G19" t="b">
-        <v>1</v>
+        <v>MRI Brain</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -2021,12 +2700,12 @@
       <c r="N19" t="b">
         <v>1</v>
       </c>
-      <c r="O19" t="str">
+      <c r="O19" t="b">
+        <v>1</v>
+      </c>
+      <c r="P19" t="str">
         <v>not_required</v>
       </c>
-      <c r="P19" t="str">
-        <v/>
-      </c>
       <c r="Q19" t="str">
         <v/>
       </c>
@@ -2034,48 +2713,60 @@
         <v/>
       </c>
       <c r="S19" t="str">
-        <v>urgently_wants_earlier</v>
+        <v/>
       </c>
       <c r="T19" t="str">
-        <v>any_earlier</v>
+        <v>neutral</v>
       </c>
       <c r="U19" t="str">
+        <v>seven_days_earlier</v>
+      </c>
+      <c r="V19" t="str">
         <v>can_move</v>
       </c>
-      <c r="V19">
-        <v>0.75</v>
-      </c>
-      <c r="W19" t="str">
-        <v>2026-06-03T18:18:36.896Z</v>
+      <c r="W19">
+        <v>0.5</v>
       </c>
       <c r="X19" t="str">
+        <v>2026-05-25T22:34:25.011Z</v>
+      </c>
+      <c r="Y19" t="str">
+        <v/>
+      </c>
+      <c r="Z19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="str">
+        <v/>
+      </c>
+      <c r="AB19" t="str">
         <v>import</v>
       </c>
-      <c r="Y19" t="str">
-        <v>2026-06-06T18:18:36.904Z</v>
+      <c r="AC19" t="str">
+        <v>2026-06-06T22:34:25.023Z</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>cust_julia</v>
+        <v>cust_tobias</v>
       </c>
       <c r="B20" t="str">
-        <v>Julia Steiner</v>
+        <v>Tobias Ehrlich</v>
       </c>
       <c r="C20" t="str">
-        <v>+43 676 188 02 17</v>
+        <v>+43 660 411 92 33</v>
       </c>
       <c r="D20" t="str">
-        <v>julia.steiner@chello.at</v>
+        <v>tobias.ehrlich@gmx.at</v>
       </c>
       <c r="E20" t="str">
         <v>de</v>
       </c>
       <c r="F20" t="str">
-        <v>Ultrasound</v>
-      </c>
-      <c r="G20" t="b">
-        <v>1</v>
+        <v>CT Chest</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -2098,12 +2789,12 @@
       <c r="N20" t="b">
         <v>1</v>
       </c>
-      <c r="O20" t="str">
+      <c r="O20" t="b">
+        <v>1</v>
+      </c>
+      <c r="P20" t="str">
         <v>not_required</v>
       </c>
-      <c r="P20" t="str">
-        <v/>
-      </c>
       <c r="Q20" t="str">
         <v/>
       </c>
@@ -2111,48 +2802,60 @@
         <v/>
       </c>
       <c r="S20" t="str">
-        <v>satisfied</v>
+        <v/>
       </c>
       <c r="T20" t="str">
-        <v>none</v>
+        <v>urgently_wants_earlier</v>
       </c>
       <c r="U20" t="str">
-        <v>do_not_move</v>
-      </c>
-      <c r="V20">
-        <v>0.4</v>
-      </c>
-      <c r="W20" t="str">
-        <v/>
+        <v>any_earlier</v>
+      </c>
+      <c r="V20" t="str">
+        <v>can_move</v>
+      </c>
+      <c r="W20">
+        <v>0.75</v>
       </c>
       <c r="X20" t="str">
+        <v>2026-06-03T22:34:25.011Z</v>
+      </c>
+      <c r="Y20" t="str">
+        <v/>
+      </c>
+      <c r="Z20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="str">
+        <v/>
+      </c>
+      <c r="AB20" t="str">
         <v>import</v>
       </c>
-      <c r="Y20" t="str">
-        <v>2026-06-06T18:18:36.904Z</v>
+      <c r="AC20" t="str">
+        <v>2026-06-06T22:34:25.023Z</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>cust_yusuf</v>
+        <v>cust_julia</v>
       </c>
       <c r="B21" t="str">
-        <v>Yusuf Kaplan</v>
+        <v>Julia Steiner</v>
       </c>
       <c r="C21" t="str">
-        <v>+43 660 711 02 36</v>
+        <v>+43 676 188 02 17</v>
       </c>
       <c r="D21" t="str">
-        <v>yusuf.kaplan@yandex.com</v>
+        <v>julia.steiner@chello.at</v>
       </c>
       <c r="E21" t="str">
-        <v>tr</v>
+        <v>de</v>
       </c>
       <c r="F21" t="str">
-        <v>MRI Spine</v>
-      </c>
-      <c r="G21" t="b">
-        <v>1</v>
+        <v>Ultrasound</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -2161,7 +2864,7 @@
         <v>1</v>
       </c>
       <c r="J21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="b">
         <v>1</v>
@@ -2175,12 +2878,12 @@
       <c r="N21" t="b">
         <v>1</v>
       </c>
-      <c r="O21" t="str">
+      <c r="O21" t="b">
+        <v>1</v>
+      </c>
+      <c r="P21" t="str">
         <v>not_required</v>
       </c>
-      <c r="P21" t="str">
-        <v/>
-      </c>
       <c r="Q21" t="str">
         <v/>
       </c>
@@ -2188,114 +2891,227 @@
         <v/>
       </c>
       <c r="S21" t="str">
-        <v>neutral</v>
+        <v/>
       </c>
       <c r="T21" t="str">
-        <v>any_earlier</v>
+        <v>satisfied</v>
       </c>
       <c r="U21" t="str">
-        <v>can_move</v>
-      </c>
-      <c r="V21">
-        <v>0.5</v>
-      </c>
-      <c r="W21" t="str">
-        <v>2026-05-20T18:18:36.896Z</v>
+        <v>none</v>
+      </c>
+      <c r="V21" t="str">
+        <v>do_not_move</v>
+      </c>
+      <c r="W21">
+        <v>0.4</v>
       </c>
       <c r="X21" t="str">
+        <v/>
+      </c>
+      <c r="Y21" t="str">
+        <v/>
+      </c>
+      <c r="Z21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="str">
+        <v/>
+      </c>
+      <c r="AB21" t="str">
         <v>import</v>
       </c>
-      <c r="Y21" t="str">
-        <v>2026-06-06T18:18:36.904Z</v>
+      <c r="AC21" t="str">
+        <v>2026-06-06T22:34:25.023Z</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
+        <v>cust_yusuf</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Yusuf Kaplan</v>
+      </c>
+      <c r="C22" t="str">
+        <v>+43 660 711 02 36</v>
+      </c>
+      <c r="D22" t="str">
+        <v>yusuf.kaplan@yandex.com</v>
+      </c>
+      <c r="E22" t="str">
+        <v>tr</v>
+      </c>
+      <c r="F22" t="str">
+        <v>MRI Spine</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="b">
+        <v>1</v>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" t="b">
+        <v>1</v>
+      </c>
+      <c r="N22" t="b">
+        <v>1</v>
+      </c>
+      <c r="O22" t="b">
+        <v>1</v>
+      </c>
+      <c r="P22" t="str">
+        <v>not_required</v>
+      </c>
+      <c r="Q22" t="str">
+        <v/>
+      </c>
+      <c r="R22" t="str">
+        <v/>
+      </c>
+      <c r="S22" t="str">
+        <v/>
+      </c>
+      <c r="T22" t="str">
+        <v>neutral</v>
+      </c>
+      <c r="U22" t="str">
+        <v>any_earlier</v>
+      </c>
+      <c r="V22" t="str">
+        <v>can_move</v>
+      </c>
+      <c r="W22">
+        <v>0.5</v>
+      </c>
+      <c r="X22" t="str">
+        <v>2026-05-20T22:34:25.011Z</v>
+      </c>
+      <c r="Y22" t="str">
+        <v/>
+      </c>
+      <c r="Z22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="str">
+        <v/>
+      </c>
+      <c r="AB22" t="str">
+        <v>import</v>
+      </c>
+      <c r="AC22" t="str">
+        <v>2026-06-06T22:34:25.023Z</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
         <v>cust_lara</v>
       </c>
-      <c r="B22" t="str">
+      <c r="B23" t="str">
         <v>Lara Bauer</v>
       </c>
-      <c r="C22" t="str">
+      <c r="C23" t="str">
         <v>+43 699 222 41 70</v>
       </c>
-      <c r="D22" t="str">
+      <c r="D23" t="str">
         <v>lara.bauer@gmail.com</v>
       </c>
-      <c r="E22" t="str">
+      <c r="E23" t="str">
         <v>de</v>
       </c>
-      <c r="F22" t="str">
+      <c r="F23" t="str">
         <v>MRI Knee</v>
       </c>
-      <c r="G22" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22" t="b">
-        <v>0</v>
-      </c>
-      <c r="I22" t="b">
-        <v>0</v>
-      </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" t="b">
-        <v>0</v>
-      </c>
-      <c r="M22" t="b">
-        <v>0</v>
-      </c>
-      <c r="N22" t="b">
-        <v>0</v>
-      </c>
-      <c r="O22" t="str">
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" t="b">
+        <v>0</v>
+      </c>
+      <c r="O23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P23" t="str">
         <v>pending</v>
       </c>
-      <c r="P22" t="str">
-        <v/>
-      </c>
-      <c r="Q22" t="str">
-        <v/>
-      </c>
-      <c r="R22" t="str">
-        <v/>
-      </c>
-      <c r="S22" t="str">
+      <c r="Q23" t="str">
+        <v/>
+      </c>
+      <c r="R23" t="str">
+        <v/>
+      </c>
+      <c r="S23" t="str">
+        <v/>
+      </c>
+      <c r="T23" t="str">
         <v>neutral</v>
       </c>
-      <c r="T22" t="str">
+      <c r="U23" t="str">
         <v>none</v>
       </c>
-      <c r="U22" t="str">
+      <c r="V23" t="str">
         <v>do_not_move</v>
       </c>
-      <c r="V22">
+      <c r="W23">
         <v>0.3</v>
       </c>
-      <c r="W22" t="str">
-        <v/>
-      </c>
-      <c r="X22" t="str">
+      <c r="X23" t="str">
+        <v/>
+      </c>
+      <c r="Y23" t="str">
+        <v/>
+      </c>
+      <c r="Z23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA23" t="str">
+        <v/>
+      </c>
+      <c r="AB23" t="str">
         <v>import</v>
       </c>
-      <c r="Y22" t="str">
-        <v>2026-06-06T18:18:36.904Z</v>
+      <c r="AC23" t="str">
+        <v>2026-06-06T22:34:25.023Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AC23"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:O20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2337,6 +3153,12 @@
       <c r="M1" t="str">
         <v>current_customer_id</v>
       </c>
+      <c r="N1" t="str">
+        <v>cascade_depth</v>
+      </c>
+      <c r="O1" t="str">
+        <v>parent_slot_id</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -2349,7 +3171,7 @@
         <v>Vienna Private Imaging — Innere Stadt</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-06T14:30:00.000Z</v>
+        <v>2026-06-07T14:30:00.000Z</v>
       </c>
       <c r="E2">
         <v>45</v>
@@ -2377,6 +3199,12 @@
       </c>
       <c r="M2" t="str">
         <v>cust_lena</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -2390,7 +3218,7 @@
         <v>Vienna Private Imaging — Innere Stadt</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-06-06T07:00:00.000Z</v>
+        <v>2026-06-07T07:00:00.000Z</v>
       </c>
       <c r="E3">
         <v>45</v>
@@ -2418,6 +3246,12 @@
       </c>
       <c r="M3" t="str">
         <v>cust_helena</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -2431,7 +3265,7 @@
         <v>Vienna Private Imaging — Innere Stadt</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-06-06T08:15:00.000Z</v>
+        <v>2026-06-07T08:15:00.000Z</v>
       </c>
       <c r="E4">
         <v>30</v>
@@ -2459,6 +3293,12 @@
       </c>
       <c r="M4" t="str">
         <v>cust_tobias</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -2472,7 +3312,7 @@
         <v>Vienna Private Imaging — Innere Stadt</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-06-06T09:30:00.000Z</v>
+        <v>2026-06-07T09:30:00.000Z</v>
       </c>
       <c r="E5">
         <v>25</v>
@@ -2500,6 +3340,12 @@
       </c>
       <c r="M5" t="str">
         <v>cust_emma</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -2513,7 +3359,7 @@
         <v>Vienna Private Imaging — Mariahilf</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-06-06T12:00:00.000Z</v>
+        <v>2026-06-07T12:00:00.000Z</v>
       </c>
       <c r="E6">
         <v>15</v>
@@ -2541,6 +3387,12 @@
       </c>
       <c r="M6" t="str">
         <v>cust_david</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -2554,7 +3406,7 @@
         <v>Vienna Private Imaging — Innere Stadt</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-06-06T13:00:00.000Z</v>
+        <v>2026-06-07T13:00:00.000Z</v>
       </c>
       <c r="E7">
         <v>60</v>
@@ -2582,6 +3434,12 @@
       </c>
       <c r="M7" t="str">
         <v>cust_paul</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -2595,7 +3453,7 @@
         <v>Vienna Private Imaging — Innere Stadt</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-06-06T15:15:00.000Z</v>
+        <v>2026-06-07T15:15:00.000Z</v>
       </c>
       <c r="E8">
         <v>30</v>
@@ -2623,6 +3481,12 @@
       </c>
       <c r="M8" t="str">
         <v>cust_clara</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -2636,7 +3500,7 @@
         <v>Vienna Private Imaging — Innere Stadt</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-06-06T16:00:00.000Z</v>
+        <v>2026-06-07T16:00:00.000Z</v>
       </c>
       <c r="E9">
         <v>45</v>
@@ -2664,6 +3528,12 @@
       </c>
       <c r="M9" t="str">
         <v>cust_finn</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -2677,7 +3547,7 @@
         <v>Vienna Private Imaging — Innere Stadt</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-06-07T07:00:00.000Z</v>
+        <v>2026-06-08T07:00:00.000Z</v>
       </c>
       <c r="E10">
         <v>45</v>
@@ -2705,6 +3575,12 @@
       </c>
       <c r="M10" t="str">
         <v>cust_isabella</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -2718,7 +3594,7 @@
         <v>Vienna Private Imaging — Innere Stadt</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-06-07T08:30:00.000Z</v>
+        <v>2026-06-08T08:30:00.000Z</v>
       </c>
       <c r="E11">
         <v>45</v>
@@ -2746,6 +3622,12 @@
       </c>
       <c r="M11" t="str">
         <v>cust_anna</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -2759,7 +3641,7 @@
         <v>Vienna Private Imaging — Innere Stadt</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-06-07T10:00:00.000Z</v>
+        <v>2026-06-08T10:00:00.000Z</v>
       </c>
       <c r="E12">
         <v>30</v>
@@ -2787,6 +3669,12 @@
       </c>
       <c r="M12" t="str">
         <v>cust_kerem</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -2800,7 +3688,7 @@
         <v>Vienna Private Imaging — Mariahilf</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-06-07T12:00:00.000Z</v>
+        <v>2026-06-08T12:00:00.000Z</v>
       </c>
       <c r="E13">
         <v>60</v>
@@ -2828,6 +3716,12 @@
       </c>
       <c r="M13" t="str">
         <v>cust_yusuf</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -2841,7 +3735,7 @@
         <v>Vienna Private Imaging — Innere Stadt</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-07-20T09:00:00.000Z</v>
+        <v>2026-07-21T09:00:00.000Z</v>
       </c>
       <c r="E14">
         <v>45</v>
@@ -2869,6 +3763,12 @@
       </c>
       <c r="M14" t="str">
         <v>cust_alex</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -2882,7 +3782,7 @@
         <v>Vienna Private Imaging — Innere Stadt</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-07-25T07:30:00.000Z</v>
+        <v>2026-07-26T07:30:00.000Z</v>
       </c>
       <c r="E15">
         <v>45</v>
@@ -2910,6 +3810,12 @@
       </c>
       <c r="M15" t="str">
         <v>cust_sara</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -2923,7 +3829,7 @@
         <v>Vienna Private Imaging — Mariahilf</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-08-02T12:00:00.000Z</v>
+        <v>2026-08-03T12:00:00.000Z</v>
       </c>
       <c r="E16">
         <v>45</v>
@@ -2951,6 +3857,12 @@
       </c>
       <c r="M16" t="str">
         <v>cust_jonas</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -2964,7 +3876,7 @@
         <v>Vienna Private Imaging — Innere Stadt</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-06-05T08:00:00.000Z</v>
+        <v>2026-06-06T08:00:00.000Z</v>
       </c>
       <c r="E17">
         <v>45</v>
@@ -2992,6 +3904,12 @@
       </c>
       <c r="M17" t="str">
         <v>cust_helena</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -3005,7 +3923,7 @@
         <v>Vienna Private Imaging — Innere Stadt</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-06-04T12:30:00.000Z</v>
+        <v>2026-06-05T12:30:00.000Z</v>
       </c>
       <c r="E18">
         <v>30</v>
@@ -3033,6 +3951,12 @@
       </c>
       <c r="M18" t="str">
         <v>cust_clara</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -3046,7 +3970,7 @@
         <v>Vienna Private Imaging — Innere Stadt</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-06-03T09:00:00.000Z</v>
+        <v>2026-06-04T09:00:00.000Z</v>
       </c>
       <c r="E19">
         <v>60</v>
@@ -3074,6 +3998,12 @@
       </c>
       <c r="M19" t="str">
         <v>cust_paul</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -3087,7 +4017,7 @@
         <v>Vienna Private Imaging — Innere Stadt</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-06-05T15:00:00.000Z</v>
+        <v>2026-06-06T15:00:00.000Z</v>
       </c>
       <c r="E20">
         <v>45</v>
@@ -3116,533 +4046,916 @@
       <c r="M20" t="str">
         <v/>
       </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O20"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:N19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>waitlist_id</v>
+      </c>
+      <c r="B1" t="str">
         <v>customer_id</v>
       </c>
-      <c r="B1" t="str">
+      <c r="C1" t="str">
+        <v>customer_name</v>
+      </c>
+      <c r="D1" t="str">
         <v>service</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>type</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>urgency_score</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>business_priority</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>preference_match</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>waiting_since</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
+        <v>last_contacted_at</v>
+      </c>
+      <c r="K1" t="str">
+        <v>can_arrive_same_day</v>
+      </c>
+      <c r="L1" t="str">
+        <v>max_travel_minutes</v>
+      </c>
+      <c r="M1" t="str">
+        <v>route_feasible_when_60m_left</v>
+      </c>
+      <c r="N1" t="str">
         <v>status</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>cust_mia</v>
+        <v>wl_001</v>
       </c>
       <c r="B2" t="str">
+        <v>cust_cagan</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Çağan Oflazoğlu</v>
+      </c>
+      <c r="D2" t="str">
         <v>MRI Knee</v>
       </c>
-      <c r="C2" t="str">
+      <c r="E2" t="str">
         <v>pure_waitlist</v>
       </c>
-      <c r="D2">
+      <c r="F2">
+        <v>0.95</v>
+      </c>
+      <c r="G2">
+        <v>0.95</v>
+      </c>
+      <c r="H2">
         <v>0.5</v>
       </c>
-      <c r="E2">
-        <v>0.6</v>
-      </c>
-      <c r="F2">
-        <v>0.5</v>
-      </c>
-      <c r="G2" t="str">
-        <v>2026-05-23T18:18:36.896Z</v>
-      </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
+        <v>2026-06-05T22:34:25.011Z</v>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>60</v>
+      </c>
+      <c r="M2" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="N2" t="str">
         <v>active</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>cust_omar</v>
+        <v>wl_002</v>
       </c>
       <c r="B3" t="str">
+        <v>cust_mia</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Mia Novak</v>
+      </c>
+      <c r="D3" t="str">
         <v>MRI Knee</v>
       </c>
-      <c r="C3" t="str">
+      <c r="E3" t="str">
         <v>pure_waitlist</v>
-      </c>
-      <c r="D3">
-        <v>0.5</v>
-      </c>
-      <c r="E3">
-        <v>0.55</v>
       </c>
       <c r="F3">
         <v>0.5</v>
       </c>
-      <c r="G3" t="str">
-        <v>2026-05-28T18:18:36.896Z</v>
-      </c>
-      <c r="H3" t="str">
+      <c r="G3">
+        <v>0.6</v>
+      </c>
+      <c r="H3">
+        <v>0.5</v>
+      </c>
+      <c r="I3" t="str">
+        <v>2026-05-23T22:34:25.011Z</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>45</v>
+      </c>
+      <c r="M3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="N3" t="str">
         <v>active</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>cust_lena</v>
+        <v>wl_003</v>
       </c>
       <c r="B4" t="str">
+        <v>cust_omar</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Omar Demir</v>
+      </c>
+      <c r="D4" t="str">
         <v>MRI Knee</v>
       </c>
-      <c r="C4" t="str">
+      <c r="E4" t="str">
         <v>pure_waitlist</v>
-      </c>
-      <c r="D4">
-        <v>0.5</v>
-      </c>
-      <c r="E4">
-        <v>0.4</v>
       </c>
       <c r="F4">
         <v>0.5</v>
       </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
+      <c r="G4">
+        <v>0.55</v>
+      </c>
+      <c r="H4">
+        <v>0.5</v>
+      </c>
+      <c r="I4" t="str">
+        <v>2026-05-28T22:34:25.011Z</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>30</v>
+      </c>
+      <c r="M4" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="N4" t="str">
         <v>active</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>cust_helena</v>
+        <v>wl_004</v>
       </c>
       <c r="B5" t="str">
-        <v>MRI Brain</v>
+        <v>cust_lena</v>
       </c>
       <c r="C5" t="str">
+        <v>Lena Brunner</v>
+      </c>
+      <c r="D5" t="str">
+        <v>MRI Knee</v>
+      </c>
+      <c r="E5" t="str">
         <v>pure_waitlist</v>
-      </c>
-      <c r="D5">
-        <v>0.5</v>
-      </c>
-      <c r="E5">
-        <v>0.65</v>
       </c>
       <c r="F5">
         <v>0.5</v>
       </c>
-      <c r="G5" t="str">
-        <v>2026-05-16T18:18:36.896Z</v>
-      </c>
-      <c r="H5" t="str">
+      <c r="G5">
+        <v>0.4</v>
+      </c>
+      <c r="H5">
+        <v>0.5</v>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>30</v>
+      </c>
+      <c r="M5" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="N5" t="str">
         <v>active</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>cust_kerem</v>
+        <v>wl_005</v>
       </c>
       <c r="B6" t="str">
-        <v>CT Chest</v>
+        <v>cust_helena</v>
       </c>
       <c r="C6" t="str">
+        <v>Helena Vogel</v>
+      </c>
+      <c r="D6" t="str">
+        <v>MRI Brain</v>
+      </c>
+      <c r="E6" t="str">
         <v>pure_waitlist</v>
-      </c>
-      <c r="D6">
-        <v>0.5</v>
-      </c>
-      <c r="E6">
-        <v>0.5</v>
       </c>
       <c r="F6">
         <v>0.5</v>
       </c>
-      <c r="G6" t="str">
-        <v>2026-05-30T18:18:36.896Z</v>
-      </c>
-      <c r="H6" t="str">
+      <c r="G6">
+        <v>0.65</v>
+      </c>
+      <c r="H6">
+        <v>0.5</v>
+      </c>
+      <c r="I6" t="str">
+        <v>2026-05-16T22:34:25.011Z</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>25</v>
+      </c>
+      <c r="M6" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="N6" t="str">
         <v>active</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>cust_isabella</v>
+        <v>wl_006</v>
       </c>
       <c r="B7" t="str">
-        <v>MRI Spine</v>
+        <v>cust_kerem</v>
       </c>
       <c r="C7" t="str">
+        <v>Kerem Yıldız</v>
+      </c>
+      <c r="D7" t="str">
+        <v>CT Chest</v>
+      </c>
+      <c r="E7" t="str">
         <v>pure_waitlist</v>
-      </c>
-      <c r="D7">
-        <v>0.5</v>
-      </c>
-      <c r="E7">
-        <v>0.6</v>
       </c>
       <c r="F7">
         <v>0.5</v>
       </c>
-      <c r="G7" t="str">
-        <v>2026-05-21T18:18:36.896Z</v>
-      </c>
-      <c r="H7" t="str">
+      <c r="G7">
+        <v>0.5</v>
+      </c>
+      <c r="H7">
+        <v>0.5</v>
+      </c>
+      <c r="I7" t="str">
+        <v>2026-05-30T22:34:25.011Z</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>40</v>
+      </c>
+      <c r="M7" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="N7" t="str">
         <v>active</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>cust_lukas</v>
+        <v>wl_007</v>
       </c>
       <c r="B8" t="str">
-        <v>MRI Knee</v>
+        <v>cust_isabella</v>
       </c>
       <c r="C8" t="str">
+        <v>Isabella Moretti</v>
+      </c>
+      <c r="D8" t="str">
+        <v>MRI Spine</v>
+      </c>
+      <c r="E8" t="str">
         <v>pure_waitlist</v>
-      </c>
-      <c r="D8">
-        <v>0.5</v>
-      </c>
-      <c r="E8">
-        <v>0.5</v>
       </c>
       <c r="F8">
         <v>0.5</v>
       </c>
-      <c r="G8" t="str">
-        <v>2026-05-24T18:18:36.896Z</v>
-      </c>
-      <c r="H8" t="str">
+      <c r="G8">
+        <v>0.6</v>
+      </c>
+      <c r="H8">
+        <v>0.5</v>
+      </c>
+      <c r="I8" t="str">
+        <v>2026-05-21T22:34:25.011Z</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>35</v>
+      </c>
+      <c r="M8" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="N8" t="str">
         <v>active</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>cust_clara</v>
+        <v>wl_008</v>
       </c>
       <c r="B9" t="str">
-        <v>CT Abdomen</v>
+        <v>cust_lukas</v>
       </c>
       <c r="C9" t="str">
+        <v>Lukas Hofer</v>
+      </c>
+      <c r="D9" t="str">
+        <v>MRI Knee</v>
+      </c>
+      <c r="E9" t="str">
         <v>pure_waitlist</v>
-      </c>
-      <c r="D9">
-        <v>0.5</v>
-      </c>
-      <c r="E9">
-        <v>0.72</v>
       </c>
       <c r="F9">
         <v>0.5</v>
       </c>
-      <c r="G9" t="str">
-        <v>2026-06-01T18:18:36.896Z</v>
-      </c>
-      <c r="H9" t="str">
+      <c r="G9">
+        <v>0.5</v>
+      </c>
+      <c r="H9">
+        <v>0.5</v>
+      </c>
+      <c r="I9" t="str">
+        <v>2026-05-24T22:34:25.011Z</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>30</v>
+      </c>
+      <c r="M9" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="N9" t="str">
         <v>active</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>cust_paul</v>
+        <v>wl_009</v>
       </c>
       <c r="B10" t="str">
-        <v>MRI Spine</v>
+        <v>cust_clara</v>
       </c>
       <c r="C10" t="str">
+        <v>Clara Pichler</v>
+      </c>
+      <c r="D10" t="str">
+        <v>CT Abdomen</v>
+      </c>
+      <c r="E10" t="str">
         <v>pure_waitlist</v>
       </c>
-      <c r="D10">
+      <c r="F10">
+        <v>0.95</v>
+      </c>
+      <c r="G10">
+        <v>0.72</v>
+      </c>
+      <c r="H10">
         <v>0.5</v>
       </c>
-      <c r="E10">
-        <v>0.55</v>
-      </c>
-      <c r="F10">
-        <v>0.5</v>
-      </c>
-      <c r="G10" t="str">
-        <v>2026-05-18T18:18:36.896Z</v>
-      </c>
-      <c r="H10" t="str">
+      <c r="I10" t="str">
+        <v>2026-06-01T22:34:25.011Z</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>50</v>
+      </c>
+      <c r="M10" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="N10" t="str">
         <v>active</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>cust_emma</v>
+        <v>wl_010</v>
       </c>
       <c r="B11" t="str">
-        <v>Ultrasound</v>
+        <v>cust_paul</v>
       </c>
       <c r="C11" t="str">
+        <v>Paul Kovač</v>
+      </c>
+      <c r="D11" t="str">
+        <v>MRI Spine</v>
+      </c>
+      <c r="E11" t="str">
         <v>pure_waitlist</v>
-      </c>
-      <c r="D11">
-        <v>0.5</v>
-      </c>
-      <c r="E11">
-        <v>0.45</v>
       </c>
       <c r="F11">
         <v>0.5</v>
       </c>
-      <c r="G11" t="str">
-        <v>2026-06-02T18:18:36.896Z</v>
-      </c>
-      <c r="H11" t="str">
+      <c r="G11">
+        <v>0.55</v>
+      </c>
+      <c r="H11">
+        <v>0.5</v>
+      </c>
+      <c r="I11" t="str">
+        <v>2026-05-18T22:34:25.011Z</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>30</v>
+      </c>
+      <c r="M11" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="N11" t="str">
         <v>active</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>cust_finn</v>
+        <v>wl_011</v>
       </c>
       <c r="B12" t="str">
-        <v>MRI Brain</v>
+        <v>cust_emma</v>
       </c>
       <c r="C12" t="str">
+        <v>Emma Schreiner</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Ultrasound</v>
+      </c>
+      <c r="E12" t="str">
         <v>pure_waitlist</v>
-      </c>
-      <c r="D12">
-        <v>0.5</v>
-      </c>
-      <c r="E12">
-        <v>0.6</v>
       </c>
       <c r="F12">
         <v>0.5</v>
       </c>
-      <c r="G12" t="str">
-        <v>2026-05-29T18:18:36.896Z</v>
-      </c>
-      <c r="H12" t="str">
+      <c r="G12">
+        <v>0.45</v>
+      </c>
+      <c r="H12">
+        <v>0.5</v>
+      </c>
+      <c r="I12" t="str">
+        <v>2026-06-02T22:34:25.011Z</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>25</v>
+      </c>
+      <c r="M12" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="N12" t="str">
         <v>active</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>cust_zeynep</v>
+        <v>wl_012</v>
       </c>
       <c r="B13" t="str">
-        <v>MRI Knee</v>
+        <v>cust_finn</v>
       </c>
       <c r="C13" t="str">
+        <v>Finn Rauch</v>
+      </c>
+      <c r="D13" t="str">
+        <v>MRI Brain</v>
+      </c>
+      <c r="E13" t="str">
         <v>pure_waitlist</v>
-      </c>
-      <c r="D13">
-        <v>0.5</v>
-      </c>
-      <c r="E13">
-        <v>0.68</v>
       </c>
       <c r="F13">
         <v>0.5</v>
       </c>
-      <c r="G13" t="str">
-        <v>2026-06-04T18:18:36.896Z</v>
-      </c>
-      <c r="H13" t="str">
+      <c r="G13">
+        <v>0.6</v>
+      </c>
+      <c r="H13">
+        <v>0.5</v>
+      </c>
+      <c r="I13" t="str">
+        <v>2026-05-29T22:34:25.011Z</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>40</v>
+      </c>
+      <c r="M13" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="N13" t="str">
         <v>active</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>cust_david</v>
+        <v>wl_013</v>
       </c>
       <c r="B14" t="str">
-        <v>X-ray</v>
+        <v>cust_zeynep</v>
       </c>
       <c r="C14" t="str">
+        <v>Zeynep Aslan</v>
+      </c>
+      <c r="D14" t="str">
+        <v>MRI Knee</v>
+      </c>
+      <c r="E14" t="str">
         <v>pure_waitlist</v>
       </c>
-      <c r="D14">
+      <c r="F14">
+        <v>0.95</v>
+      </c>
+      <c r="G14">
+        <v>0.68</v>
+      </c>
+      <c r="H14">
         <v>0.5</v>
       </c>
-      <c r="E14">
-        <v>0.4</v>
-      </c>
-      <c r="F14">
-        <v>0.5</v>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
+      <c r="I14" t="str">
+        <v>2026-06-04T22:34:25.011Z</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>35</v>
+      </c>
+      <c r="M14" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="N14" t="str">
         <v>active</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>cust_anna</v>
+        <v>wl_014</v>
       </c>
       <c r="B15" t="str">
-        <v>MRI Brain</v>
+        <v>cust_david</v>
       </c>
       <c r="C15" t="str">
+        <v>David Marković</v>
+      </c>
+      <c r="D15" t="str">
+        <v>X-ray</v>
+      </c>
+      <c r="E15" t="str">
         <v>pure_waitlist</v>
-      </c>
-      <c r="D15">
-        <v>0.5</v>
-      </c>
-      <c r="E15">
-        <v>0.5</v>
       </c>
       <c r="F15">
         <v>0.5</v>
       </c>
-      <c r="G15" t="str">
-        <v>2026-05-25T18:18:36.896Z</v>
-      </c>
-      <c r="H15" t="str">
+      <c r="G15">
+        <v>0.4</v>
+      </c>
+      <c r="H15">
+        <v>0.5</v>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>30</v>
+      </c>
+      <c r="M15" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="N15" t="str">
         <v>active</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>cust_tobias</v>
+        <v>wl_015</v>
       </c>
       <c r="B16" t="str">
-        <v>CT Chest</v>
+        <v>cust_anna</v>
       </c>
       <c r="C16" t="str">
+        <v>Anna Greiner</v>
+      </c>
+      <c r="D16" t="str">
+        <v>MRI Brain</v>
+      </c>
+      <c r="E16" t="str">
         <v>pure_waitlist</v>
-      </c>
-      <c r="D16">
-        <v>0.5</v>
-      </c>
-      <c r="E16">
-        <v>0.75</v>
       </c>
       <c r="F16">
         <v>0.5</v>
       </c>
-      <c r="G16" t="str">
-        <v>2026-06-03T18:18:36.896Z</v>
-      </c>
-      <c r="H16" t="str">
+      <c r="G16">
+        <v>0.5</v>
+      </c>
+      <c r="H16">
+        <v>0.5</v>
+      </c>
+      <c r="I16" t="str">
+        <v>2026-05-25T22:34:25.011Z</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>60</v>
+      </c>
+      <c r="M16" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="N16" t="str">
         <v>active</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>cust_julia</v>
+        <v>wl_016</v>
       </c>
       <c r="B17" t="str">
-        <v>Ultrasound</v>
+        <v>cust_tobias</v>
       </c>
       <c r="C17" t="str">
+        <v>Tobias Ehrlich</v>
+      </c>
+      <c r="D17" t="str">
+        <v>CT Chest</v>
+      </c>
+      <c r="E17" t="str">
         <v>pure_waitlist</v>
       </c>
-      <c r="D17">
+      <c r="F17">
+        <v>0.95</v>
+      </c>
+      <c r="G17">
+        <v>0.75</v>
+      </c>
+      <c r="H17">
         <v>0.5</v>
       </c>
-      <c r="E17">
-        <v>0.4</v>
-      </c>
-      <c r="F17">
-        <v>0.5</v>
-      </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
-      <c r="H17" t="str">
+      <c r="I17" t="str">
+        <v>2026-06-03T22:34:25.011Z</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>30</v>
+      </c>
+      <c r="M17" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="N17" t="str">
         <v>active</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>cust_yusuf</v>
+        <v>wl_017</v>
       </c>
       <c r="B18" t="str">
-        <v>MRI Spine</v>
+        <v>cust_julia</v>
       </c>
       <c r="C18" t="str">
+        <v>Julia Steiner</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Ultrasound</v>
+      </c>
+      <c r="E18" t="str">
         <v>pure_waitlist</v>
-      </c>
-      <c r="D18">
-        <v>0.5</v>
-      </c>
-      <c r="E18">
-        <v>0.5</v>
       </c>
       <c r="F18">
         <v>0.5</v>
       </c>
-      <c r="G18" t="str">
-        <v>2026-05-20T18:18:36.896Z</v>
-      </c>
-      <c r="H18" t="str">
+      <c r="G18">
+        <v>0.4</v>
+      </c>
+      <c r="H18">
+        <v>0.5</v>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>25</v>
+      </c>
+      <c r="M18" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="N18" t="str">
+        <v>active</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>wl_018</v>
+      </c>
+      <c r="B19" t="str">
+        <v>cust_yusuf</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Yusuf Kaplan</v>
+      </c>
+      <c r="D19" t="str">
+        <v>MRI Spine</v>
+      </c>
+      <c r="E19" t="str">
+        <v>pure_waitlist</v>
+      </c>
+      <c r="F19">
+        <v>0.5</v>
+      </c>
+      <c r="G19">
+        <v>0.5</v>
+      </c>
+      <c r="H19">
+        <v>0.5</v>
+      </c>
+      <c r="I19" t="str">
+        <v>2026-05-20T22:34:25.011Z</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>40</v>
+      </c>
+      <c r="M19" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="N19" t="str">
         <v>active</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N19"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:K23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>customer_id</v>
       </c>
       <c r="B1" t="str">
+        <v>customer_name</v>
+      </c>
+      <c r="C1" t="str">
         <v>service</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>safety_form_complete</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>referral_received</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>payment_ready</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>authorization_approved</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>contrast_status</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>can_arrive_same_day</v>
+      </c>
+      <c r="J1" t="str">
+        <v>max_travel_minutes</v>
+      </c>
+      <c r="K1" t="str">
+        <v>eligibility_score</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>cust_alex</v>
+        <v>cust_cagan</v>
       </c>
       <c r="B2" t="str">
+        <v>Çağan Oflazoğlu</v>
+      </c>
+      <c r="C2" t="str">
         <v>MRI Knee</v>
       </c>
-      <c r="C2" t="b">
-        <v>1</v>
-      </c>
       <c r="D2" t="b">
         <v>1</v>
       </c>
@@ -3652,23 +4965,32 @@
       <c r="F2" t="b">
         <v>1</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" t="str">
         <v>not_required</v>
       </c>
-      <c r="H2" t="b">
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>60</v>
+      </c>
+      <c r="K2">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>cust_sara</v>
+        <v>cust_alex</v>
       </c>
       <c r="B3" t="str">
+        <v>Alex Berger</v>
+      </c>
+      <c r="C3" t="str">
         <v>MRI Knee</v>
       </c>
-      <c r="C3" t="b">
-        <v>1</v>
-      </c>
       <c r="D3" t="b">
         <v>1</v>
       </c>
@@ -3678,23 +5000,32 @@
       <c r="F3" t="b">
         <v>1</v>
       </c>
-      <c r="G3" t="str">
-        <v>cleared</v>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" t="str">
+        <v>not_required</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>35</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>cust_jonas</v>
+        <v>cust_sara</v>
       </c>
       <c r="B4" t="str">
+        <v>Sara Klein</v>
+      </c>
+      <c r="C4" t="str">
         <v>MRI Knee</v>
       </c>
-      <c r="C4" t="b">
-        <v>1</v>
-      </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
@@ -3704,23 +5035,32 @@
       <c r="F4" t="b">
         <v>1</v>
       </c>
-      <c r="G4" t="str">
-        <v>not_required</v>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="str">
+        <v>cleared</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>20</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>cust_mia</v>
+        <v>cust_jonas</v>
       </c>
       <c r="B5" t="str">
+        <v>Jonas Weber</v>
+      </c>
+      <c r="C5" t="str">
         <v>MRI Knee</v>
       </c>
-      <c r="C5" t="b">
-        <v>1</v>
-      </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
@@ -3730,23 +5070,32 @@
       <c r="F5" t="b">
         <v>1</v>
       </c>
-      <c r="G5" t="str">
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="str">
         <v>not_required</v>
       </c>
-      <c r="H5" t="b">
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>60</v>
+      </c>
+      <c r="K5">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>cust_omar</v>
+        <v>cust_mia</v>
       </c>
       <c r="B6" t="str">
+        <v>Mia Novak</v>
+      </c>
+      <c r="C6" t="str">
         <v>MRI Knee</v>
       </c>
-      <c r="C6" t="b">
-        <v>1</v>
-      </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
@@ -3754,25 +5103,34 @@
         <v>1</v>
       </c>
       <c r="F6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" t="str">
-        <v>pending</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" t="str">
+        <v>not_required</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>45</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>cust_lena</v>
+        <v>cust_omar</v>
       </c>
       <c r="B7" t="str">
+        <v>Omar Demir</v>
+      </c>
+      <c r="C7" t="str">
         <v>MRI Knee</v>
       </c>
-      <c r="C7" t="b">
-        <v>1</v>
-      </c>
       <c r="D7" t="b">
         <v>1</v>
       </c>
@@ -3782,22 +5140,31 @@
       <c r="F7" t="b">
         <v>1</v>
       </c>
-      <c r="G7" t="str">
-        <v>not_required</v>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="str">
+        <v>pending</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>30</v>
+      </c>
+      <c r="K7">
+        <v>0.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>cust_helena</v>
+        <v>cust_lena</v>
       </c>
       <c r="B8" t="str">
-        <v>MRI Brain</v>
-      </c>
-      <c r="C8" t="b">
-        <v>1</v>
+        <v>Lena Brunner</v>
+      </c>
+      <c r="C8" t="str">
+        <v>MRI Knee</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
@@ -3808,22 +5175,31 @@
       <c r="F8" t="b">
         <v>1</v>
       </c>
-      <c r="G8" t="str">
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="str">
         <v>not_required</v>
       </c>
-      <c r="H8" t="b">
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>30</v>
+      </c>
+      <c r="K8">
         <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>cust_kerem</v>
+        <v>cust_helena</v>
       </c>
       <c r="B9" t="str">
-        <v>CT Chest</v>
-      </c>
-      <c r="C9" t="b">
-        <v>0</v>
+        <v>Helena Vogel</v>
+      </c>
+      <c r="C9" t="str">
+        <v>MRI Brain</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
@@ -3834,48 +5210,66 @@
       <c r="F9" t="b">
         <v>1</v>
       </c>
-      <c r="G9" t="str">
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="str">
         <v>not_required</v>
       </c>
-      <c r="H9" t="b">
-        <v>0</v>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>25</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>cust_isabella</v>
+        <v>cust_kerem</v>
       </c>
       <c r="B10" t="str">
-        <v>MRI Spine</v>
-      </c>
-      <c r="C10" t="b">
-        <v>1</v>
+        <v>Kerem Yıldız</v>
+      </c>
+      <c r="C10" t="str">
+        <v>CT Chest</v>
       </c>
       <c r="D10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
       </c>
-      <c r="G10" t="str">
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="str">
         <v>not_required</v>
       </c>
-      <c r="H10" t="b">
-        <v>0</v>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>40</v>
+      </c>
+      <c r="K10">
+        <v>0.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>cust_lukas</v>
+        <v>cust_isabella</v>
       </c>
       <c r="B11" t="str">
-        <v>MRI Knee</v>
-      </c>
-      <c r="C11" t="b">
-        <v>1</v>
+        <v>Isabella Moretti</v>
+      </c>
+      <c r="C11" t="str">
+        <v>MRI Spine</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
@@ -3884,24 +5278,33 @@
         <v>1</v>
       </c>
       <c r="F11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" t="str">
+        <v>0</v>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="str">
         <v>not_required</v>
       </c>
-      <c r="H11" t="b">
-        <v>0</v>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>35</v>
+      </c>
+      <c r="K11">
+        <v>0.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>cust_clara</v>
+        <v>cust_lukas</v>
       </c>
       <c r="B12" t="str">
-        <v>CT Abdomen</v>
-      </c>
-      <c r="C12" t="b">
-        <v>1</v>
+        <v>Lukas Hofer</v>
+      </c>
+      <c r="C12" t="str">
+        <v>MRI Knee</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
@@ -3912,22 +5315,31 @@
       <c r="F12" t="b">
         <v>1</v>
       </c>
-      <c r="G12" t="str">
-        <v>cleared</v>
-      </c>
-      <c r="H12" t="b">
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="str">
+        <v>not_required</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>30</v>
+      </c>
+      <c r="K12">
         <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>cust_paul</v>
+        <v>cust_clara</v>
       </c>
       <c r="B13" t="str">
-        <v>MRI Spine</v>
-      </c>
-      <c r="C13" t="b">
-        <v>1</v>
+        <v>Clara Pichler</v>
+      </c>
+      <c r="C13" t="str">
+        <v>CT Abdomen</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
@@ -3938,22 +5350,31 @@
       <c r="F13" t="b">
         <v>1</v>
       </c>
-      <c r="G13" t="str">
-        <v>not_required</v>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="str">
+        <v>cleared</v>
+      </c>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>50</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>cust_emma</v>
+        <v>cust_paul</v>
       </c>
       <c r="B14" t="str">
-        <v>Ultrasound</v>
-      </c>
-      <c r="C14" t="b">
-        <v>1</v>
+        <v>Paul Kovač</v>
+      </c>
+      <c r="C14" t="str">
+        <v>MRI Spine</v>
       </c>
       <c r="D14" t="b">
         <v>1</v>
@@ -3964,25 +5385,34 @@
       <c r="F14" t="b">
         <v>1</v>
       </c>
-      <c r="G14" t="str">
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="str">
         <v>not_required</v>
       </c>
-      <c r="H14" t="b">
-        <v>0</v>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>30</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>cust_finn</v>
+        <v>cust_emma</v>
       </c>
       <c r="B15" t="str">
-        <v>MRI Brain</v>
-      </c>
-      <c r="C15" t="b">
-        <v>1</v>
+        <v>Emma Schreiner</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Ultrasound</v>
       </c>
       <c r="D15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
@@ -3990,48 +5420,66 @@
       <c r="F15" t="b">
         <v>1</v>
       </c>
-      <c r="G15" t="str">
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="str">
         <v>not_required</v>
       </c>
-      <c r="H15" t="b">
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>25</v>
+      </c>
+      <c r="K15">
         <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>cust_zeynep</v>
+        <v>cust_finn</v>
       </c>
       <c r="B16" t="str">
-        <v>MRI Knee</v>
-      </c>
-      <c r="C16" t="b">
-        <v>1</v>
+        <v>Finn Rauch</v>
+      </c>
+      <c r="C16" t="str">
+        <v>MRI Brain</v>
       </c>
       <c r="D16" t="b">
         <v>1</v>
       </c>
       <c r="E16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
       </c>
-      <c r="G16" t="str">
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" t="str">
         <v>not_required</v>
       </c>
-      <c r="H16" t="b">
-        <v>1</v>
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>40</v>
+      </c>
+      <c r="K16">
+        <v>0.75</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>cust_david</v>
+        <v>cust_zeynep</v>
       </c>
       <c r="B17" t="str">
-        <v>X-ray</v>
-      </c>
-      <c r="C17" t="b">
-        <v>1</v>
+        <v>Zeynep Aslan</v>
+      </c>
+      <c r="C17" t="str">
+        <v>MRI Knee</v>
       </c>
       <c r="D17" t="b">
         <v>1</v>
@@ -4042,22 +5490,31 @@
       <c r="F17" t="b">
         <v>1</v>
       </c>
-      <c r="G17" t="str">
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" t="str">
         <v>not_required</v>
       </c>
-      <c r="H17" t="b">
-        <v>0</v>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>35</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>cust_anna</v>
+        <v>cust_david</v>
       </c>
       <c r="B18" t="str">
-        <v>MRI Brain</v>
-      </c>
-      <c r="C18" t="b">
-        <v>1</v>
+        <v>David Marković</v>
+      </c>
+      <c r="C18" t="str">
+        <v>X-ray</v>
       </c>
       <c r="D18" t="b">
         <v>1</v>
@@ -4068,22 +5525,31 @@
       <c r="F18" t="b">
         <v>1</v>
       </c>
-      <c r="G18" t="str">
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="str">
         <v>not_required</v>
       </c>
-      <c r="H18" t="b">
-        <v>0</v>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>30</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>cust_tobias</v>
+        <v>cust_anna</v>
       </c>
       <c r="B19" t="str">
-        <v>CT Chest</v>
-      </c>
-      <c r="C19" t="b">
-        <v>1</v>
+        <v>Anna Greiner</v>
+      </c>
+      <c r="C19" t="str">
+        <v>MRI Brain</v>
       </c>
       <c r="D19" t="b">
         <v>1</v>
@@ -4094,22 +5560,31 @@
       <c r="F19" t="b">
         <v>1</v>
       </c>
-      <c r="G19" t="str">
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="str">
         <v>not_required</v>
       </c>
-      <c r="H19" t="b">
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>60</v>
+      </c>
+      <c r="K19">
         <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>cust_julia</v>
+        <v>cust_tobias</v>
       </c>
       <c r="B20" t="str">
-        <v>Ultrasound</v>
-      </c>
-      <c r="C20" t="b">
-        <v>1</v>
+        <v>Tobias Ehrlich</v>
+      </c>
+      <c r="C20" t="str">
+        <v>CT Chest</v>
       </c>
       <c r="D20" t="b">
         <v>1</v>
@@ -4120,22 +5595,31 @@
       <c r="F20" t="b">
         <v>1</v>
       </c>
-      <c r="G20" t="str">
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" t="str">
         <v>not_required</v>
       </c>
-      <c r="H20" t="b">
-        <v>0</v>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>30</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>cust_yusuf</v>
+        <v>cust_julia</v>
       </c>
       <c r="B21" t="str">
-        <v>MRI Spine</v>
-      </c>
-      <c r="C21" t="b">
-        <v>1</v>
+        <v>Julia Steiner</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Ultrasound</v>
       </c>
       <c r="D21" t="b">
         <v>1</v>
@@ -4146,49 +5630,102 @@
       <c r="F21" t="b">
         <v>1</v>
       </c>
-      <c r="G21" t="str">
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" t="str">
         <v>not_required</v>
       </c>
-      <c r="H21" t="b">
-        <v>0</v>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>25</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
+        <v>cust_yusuf</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Yusuf Kaplan</v>
+      </c>
+      <c r="C22" t="str">
+        <v>MRI Spine</v>
+      </c>
+      <c r="D22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" t="str">
+        <v>not_required</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>40</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
         <v>cust_lara</v>
       </c>
-      <c r="B22" t="str">
+      <c r="B23" t="str">
+        <v>Lara Bauer</v>
+      </c>
+      <c r="C23" t="str">
         <v>MRI Knee</v>
       </c>
-      <c r="C22" t="b">
-        <v>0</v>
-      </c>
-      <c r="D22" t="b">
-        <v>0</v>
-      </c>
-      <c r="E22" t="b">
-        <v>0</v>
-      </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" t="str">
+      <c r="D23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" t="str">
         <v>pending</v>
       </c>
-      <c r="H22" t="b">
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>20</v>
+      </c>
+      <c r="K23">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K23"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4209,6 +5746,24 @@
       <c r="F1" t="str">
         <v>duration_seconds</v>
       </c>
+      <c r="G1" t="str">
+        <v>slot_accepted</v>
+      </c>
+      <c r="H1" t="str">
+        <v>identity_confirmed</v>
+      </c>
+      <c r="I1" t="str">
+        <v>asked_medical_question</v>
+      </c>
+      <c r="J1" t="str">
+        <v>wants_callback</v>
+      </c>
+      <c r="K1" t="str">
+        <v>voicemail</v>
+      </c>
+      <c r="L1" t="str">
+        <v>opt_out</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -4229,6 +5784,24 @@
       <c r="F2">
         <v>78</v>
       </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -4249,10 +5822,28 @@
       <c r="F3">
         <v>64</v>
       </c>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4286,7 +5877,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-06-05T18:18:36.903Z</v>
+        <v>2026-06-05T22:34:25.021Z</v>
       </c>
       <c r="B2" t="str">
         <v>user</v>
@@ -4309,7 +5900,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-06-05T22:18:36.903Z</v>
+        <v>2026-06-06T02:34:25.021Z</v>
       </c>
       <c r="B3" t="str">
         <v>system</v>
@@ -4332,7 +5923,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-06-06T12:18:36.903Z</v>
+        <v>2026-06-06T16:34:25.021Z</v>
       </c>
       <c r="B4" t="str">
         <v>user</v>
@@ -4362,7 +5953,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4395,6 +5986,12 @@
       <c r="J1" t="str">
         <v>max_cascade_depth</v>
       </c>
+      <c r="K1" t="str">
+        <v>default_concurrent_calls</v>
+      </c>
+      <c r="L1" t="str">
+        <v>emergency_concurrent_calls</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -4427,85 +6024,211 @@
       <c r="J2">
         <v>5</v>
       </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:G8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>sheet</v>
+        <v>service</v>
       </c>
       <c r="B1" t="str">
-        <v>supabase_table</v>
+        <v>duration_minutes</v>
+      </c>
+      <c r="C1" t="str">
+        <v>value_eur</v>
+      </c>
+      <c r="D1" t="str">
+        <v>requires_referral</v>
+      </c>
+      <c r="E1" t="str">
+        <v>requires_safety_form</v>
+      </c>
+      <c r="F1" t="str">
+        <v>requires_contrast</v>
+      </c>
+      <c r="G1" t="str">
+        <v>arrival_buffer_minutes</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Customers</v>
-      </c>
-      <c r="B2" t="str">
-        <v>customers + customer_consents + customer_eligibility</v>
+        <v>MRI Knee</v>
+      </c>
+      <c r="B2">
+        <v>45</v>
+      </c>
+      <c r="C2">
+        <v>420</v>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Slots</v>
-      </c>
-      <c r="B3" t="str">
-        <v>slots</v>
+        <v>MRI Brain</v>
+      </c>
+      <c r="B3">
+        <v>45</v>
+      </c>
+      <c r="C3">
+        <v>520</v>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Waitlist</v>
-      </c>
-      <c r="B4" t="str">
-        <v>waitlist_entries</v>
+        <v>MRI Spine</v>
+      </c>
+      <c r="B4">
+        <v>60</v>
+      </c>
+      <c r="C4">
+        <v>640</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Eligibility</v>
-      </c>
-      <c r="B5" t="str">
-        <v>customer_eligibility</v>
+        <v>CT Chest</v>
+      </c>
+      <c r="B5">
+        <v>30</v>
+      </c>
+      <c r="C5">
+        <v>380</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Calls</v>
-      </c>
-      <c r="B6" t="str">
-        <v>call_attempts</v>
+        <v>CT Abdomen</v>
+      </c>
+      <c r="B6">
+        <v>30</v>
+      </c>
+      <c r="C6">
+        <v>410</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Audit_Log</v>
-      </c>
-      <c r="B7" t="str">
-        <v>audit_log</v>
+        <v>Ultrasound</v>
+      </c>
+      <c r="B7">
+        <v>25</v>
+      </c>
+      <c r="C7">
+        <v>180</v>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Rules</v>
-      </c>
-      <c r="B8" t="str">
-        <v>algorithm_rules</v>
+        <v>X-ray</v>
+      </c>
+      <c r="B8">
+        <v>15</v>
+      </c>
+      <c r="C8">
+        <v>120</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G8"/>
   </ignoredErrors>
 </worksheet>
 </file>